--- a/salidas/empresas/NKE.xlsx
+++ b/salidas/empresas/NKE.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EPS" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Info" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="EPS" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Info" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -23,13 +23,16 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -40,7 +43,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -48,12 +51,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -435,58 +447,58 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>fecha</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>precio_ajustado</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>precio_cierre</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>volumen</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>pe</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>acciones_circulacion</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>market_cap</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>rotacion</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>38748</v>
       </c>
       <c r="B2" t="n">
-        <v>7.582490921020508</v>
+        <v>7.582486152648926</v>
       </c>
       <c r="C2" t="n">
         <v>10.11874961853027</v>
@@ -501,11 +513,11 @@
       <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>38776</v>
       </c>
       <c r="B3" t="n">
-        <v>8.12857723236084</v>
+        <v>8.128575325012207</v>
       </c>
       <c r="C3" t="n">
         <v>10.84749984741211</v>
@@ -520,11 +532,11 @@
       <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>38807</v>
       </c>
       <c r="B4" t="n">
-        <v>7.985772609710693</v>
+        <v>7.985776901245117</v>
       </c>
       <c r="C4" t="n">
         <v>10.63749980926514</v>
@@ -539,11 +551,11 @@
       <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>38837</v>
       </c>
       <c r="B5" t="n">
-        <v>7.679858684539795</v>
+        <v>7.67986011505127</v>
       </c>
       <c r="C5" t="n">
         <v>10.22999954223633</v>
@@ -558,11 +570,11 @@
       <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>38868</v>
       </c>
       <c r="B6" t="n">
-        <v>7.536280632019043</v>
+        <v>7.536279201507568</v>
       </c>
       <c r="C6" t="n">
         <v>10.03874969482422</v>
@@ -577,11 +589,11 @@
       <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>38898</v>
       </c>
       <c r="B7" t="n">
-        <v>7.615652084350586</v>
+        <v>7.615654945373535</v>
       </c>
       <c r="C7" t="n">
         <v>10.125</v>
@@ -596,11 +608,11 @@
       <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>38929</v>
       </c>
       <c r="B8" t="n">
-        <v>7.427609443664551</v>
+        <v>7.427614688873291</v>
       </c>
       <c r="C8" t="n">
         <v>9.875</v>
@@ -615,7 +627,7 @@
       <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>38960</v>
       </c>
       <c r="B9" t="n">
@@ -634,11 +646,11 @@
       <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>38990</v>
       </c>
       <c r="B10" t="n">
-        <v>8.253867149353027</v>
+        <v>8.25386905670166</v>
       </c>
       <c r="C10" t="n">
         <v>10.95250034332275</v>
@@ -653,11 +665,11 @@
       <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>39021</v>
       </c>
       <c r="B11" t="n">
-        <v>8.655162811279297</v>
+        <v>8.65516185760498</v>
       </c>
       <c r="C11" t="n">
         <v>11.48499965667725</v>
@@ -672,11 +684,11 @@
       <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>39051</v>
       </c>
       <c r="B12" t="n">
-        <v>9.321157455444336</v>
+        <v>9.321163177490234</v>
       </c>
       <c r="C12" t="n">
         <v>12.36874961853027</v>
@@ -691,11 +703,11 @@
       <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>39082</v>
       </c>
       <c r="B13" t="n">
-        <v>9.346303939819336</v>
+        <v>9.346307754516602</v>
       </c>
       <c r="C13" t="n">
         <v>12.37874984741211</v>
@@ -710,11 +722,11 @@
       <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>39113</v>
       </c>
       <c r="B14" t="n">
-        <v>9.325541496276855</v>
+        <v>9.325542449951172</v>
       </c>
       <c r="C14" t="n">
         <v>12.35124969482422</v>
@@ -729,11 +741,11 @@
       <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>39141</v>
       </c>
       <c r="B15" t="n">
-        <v>9.859726905822754</v>
+        <v>9.859724044799805</v>
       </c>
       <c r="C15" t="n">
         <v>13.05875015258789</v>
@@ -748,11 +760,11 @@
       <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>39172</v>
       </c>
       <c r="B16" t="n">
-        <v>10.04643249511719</v>
+        <v>10.04642963409424</v>
       </c>
       <c r="C16" t="n">
         <v>13.28250026702881</v>
@@ -767,11 +779,11 @@
       <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>39202</v>
       </c>
       <c r="B17" t="n">
-        <v>10.18447017669678</v>
+        <v>10.18446731567383</v>
       </c>
       <c r="C17" t="n">
         <v>13.46500015258789</v>
@@ -786,11 +798,11 @@
       <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>39233</v>
       </c>
       <c r="B18" t="n">
-        <v>10.73094654083252</v>
+        <v>10.73094272613525</v>
       </c>
       <c r="C18" t="n">
         <v>14.1875</v>
@@ -805,11 +817,11 @@
       <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>39263</v>
       </c>
       <c r="B19" t="n">
-        <v>11.05886745452881</v>
+        <v>11.05886840820312</v>
       </c>
       <c r="C19" t="n">
         <v>14.57250022888184</v>
@@ -824,11 +836,11 @@
       <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>39294</v>
       </c>
       <c r="B20" t="n">
-        <v>10.70977973937988</v>
+        <v>10.70978164672852</v>
       </c>
       <c r="C20" t="n">
         <v>14.11250019073486</v>
@@ -843,11 +855,11 @@
       <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>39325</v>
       </c>
       <c r="B21" t="n">
-        <v>10.68891048431396</v>
+        <v>10.6889123916626</v>
       </c>
       <c r="C21" t="n">
         <v>14.08500003814697</v>
@@ -862,11 +874,11 @@
       <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>39355</v>
       </c>
       <c r="B22" t="n">
-        <v>11.16630744934082</v>
+        <v>11.16630458831787</v>
       </c>
       <c r="C22" t="n">
         <v>14.66499996185303</v>
@@ -881,11 +893,11 @@
       <c r="I22" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>39386</v>
       </c>
       <c r="B23" t="n">
-        <v>12.61301612854004</v>
+        <v>12.61301326751709</v>
       </c>
       <c r="C23" t="n">
         <v>16.56500053405762</v>
@@ -900,11 +912,11 @@
       <c r="I23" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>39416</v>
       </c>
       <c r="B24" t="n">
-        <v>12.49689865112305</v>
+        <v>12.49689960479736</v>
       </c>
       <c r="C24" t="n">
         <v>16.41250038146973</v>
@@ -919,11 +931,11 @@
       <c r="I24" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>39447</v>
       </c>
       <c r="B25" t="n">
-        <v>12.2712926864624</v>
+        <v>12.2712984085083</v>
       </c>
       <c r="C25" t="n">
         <v>16.05999946594238</v>
@@ -938,11 +950,11 @@
       <c r="I25" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>39478</v>
       </c>
       <c r="B26" t="n">
-        <v>11.71542358398438</v>
+        <v>11.71542453765869</v>
       </c>
       <c r="C26" t="n">
         <v>15.33250045776367</v>
@@ -957,11 +969,11 @@
       <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>39507</v>
       </c>
       <c r="B27" t="n">
-        <v>11.49956893920898</v>
+        <v>11.49957084655762</v>
       </c>
       <c r="C27" t="n">
         <v>15.05000019073486</v>
@@ -976,11 +988,11 @@
       <c r="I27" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>39538</v>
       </c>
       <c r="B28" t="n">
-        <v>13.03885364532471</v>
+        <v>13.03886032104492</v>
       </c>
       <c r="C28" t="n">
         <v>17</v>
@@ -995,7 +1007,7 @@
       <c r="I28" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>39568</v>
       </c>
       <c r="B29" t="n">
@@ -1014,11 +1026,11 @@
       <c r="I29" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>39599</v>
       </c>
       <c r="B30" t="n">
-        <v>13.10980796813965</v>
+        <v>13.10980319976807</v>
       </c>
       <c r="C30" t="n">
         <v>17.09250068664551</v>
@@ -1033,11 +1045,11 @@
       <c r="I30" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>39629</v>
       </c>
       <c r="B31" t="n">
-        <v>11.468918800354</v>
+        <v>11.46891784667969</v>
       </c>
       <c r="C31" t="n">
         <v>14.90250015258789</v>
@@ -1052,11 +1064,11 @@
       <c r="I31" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>39660</v>
       </c>
       <c r="B32" t="n">
-        <v>11.28999042510986</v>
+        <v>11.28998851776123</v>
       </c>
       <c r="C32" t="n">
         <v>14.67000007629395</v>
@@ -1071,11 +1083,11 @@
       <c r="I32" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>39691</v>
       </c>
       <c r="B33" t="n">
-        <v>11.6613187789917</v>
+        <v>11.66132068634033</v>
       </c>
       <c r="C33" t="n">
         <v>15.15250015258789</v>
@@ -1090,11 +1102,11 @@
       <c r="I33" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>39721</v>
       </c>
       <c r="B34" t="n">
-        <v>12.91950988769531</v>
+        <v>12.91950798034668</v>
       </c>
       <c r="C34" t="n">
         <v>16.72500038146973</v>
@@ -1109,7 +1121,7 @@
       <c r="I34" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>39752</v>
       </c>
       <c r="B35" t="n">
@@ -1128,11 +1140,11 @@
       <c r="I35" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>39782</v>
       </c>
       <c r="B36" t="n">
-        <v>10.28346920013428</v>
+        <v>10.28346824645996</v>
       </c>
       <c r="C36" t="n">
         <v>13.3125</v>
@@ -1147,11 +1159,11 @@
       <c r="I36" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>39813</v>
       </c>
       <c r="B37" t="n">
-        <v>9.896523475646973</v>
+        <v>9.896522521972656</v>
       </c>
       <c r="C37" t="n">
         <v>12.75</v>
@@ -1166,11 +1178,11 @@
       <c r="I37" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>39844</v>
       </c>
       <c r="B38" t="n">
-        <v>8.78073787689209</v>
+        <v>8.780738830566406</v>
       </c>
       <c r="C38" t="n">
         <v>11.3125</v>
@@ -1185,7 +1197,7 @@
       <c r="I38" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>39872</v>
       </c>
       <c r="B39" t="n">
@@ -1204,11 +1216,11 @@
       <c r="I39" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>39903</v>
       </c>
       <c r="B40" t="n">
-        <v>9.152755737304688</v>
+        <v>9.15275764465332</v>
       </c>
       <c r="C40" t="n">
         <v>11.72249984741211</v>
@@ -1223,11 +1235,11 @@
       <c r="I40" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>39933</v>
       </c>
       <c r="B41" t="n">
-        <v>10.24195098876953</v>
+        <v>10.24195003509521</v>
       </c>
       <c r="C41" t="n">
         <v>13.11750030517578</v>
@@ -1242,11 +1254,11 @@
       <c r="I41" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>39964</v>
       </c>
       <c r="B42" t="n">
-        <v>11.13595199584961</v>
+        <v>11.13595104217529</v>
       </c>
       <c r="C42" t="n">
         <v>14.26249980926514</v>
@@ -1261,7 +1273,7 @@
       <c r="I42" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>39994</v>
       </c>
       <c r="B43" t="n">
@@ -1280,7 +1292,7 @@
       <c r="I43" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>40025</v>
       </c>
       <c r="B44" t="n">
@@ -1299,11 +1311,11 @@
       <c r="I44" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>40056</v>
       </c>
       <c r="B45" t="n">
-        <v>10.85859107971191</v>
+        <v>10.85859203338623</v>
       </c>
       <c r="C45" t="n">
         <v>13.84749984741211</v>
@@ -1318,7 +1330,7 @@
       <c r="I45" t="inlineStr"/>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>40086</v>
       </c>
       <c r="B46" t="n">
@@ -1337,11 +1349,11 @@
       <c r="I46" t="inlineStr"/>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>40117</v>
       </c>
       <c r="B47" t="n">
-        <v>12.24713230133057</v>
+        <v>12.24712944030762</v>
       </c>
       <c r="C47" t="n">
         <v>15.54500007629395</v>
@@ -1362,11 +1374,11 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>40147</v>
       </c>
       <c r="B48" t="n">
-        <v>12.7809009552002</v>
+        <v>12.78089904785156</v>
       </c>
       <c r="C48" t="n">
         <v>16.22249984741211</v>
@@ -1387,11 +1399,11 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>40178</v>
       </c>
       <c r="B49" t="n">
-        <v>13.06729888916016</v>
+        <v>13.06730175018311</v>
       </c>
       <c r="C49" t="n">
         <v>16.51749992370605</v>
@@ -1412,11 +1424,11 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>40209</v>
       </c>
       <c r="B50" t="n">
-        <v>12.60845565795898</v>
+        <v>12.60844898223877</v>
       </c>
       <c r="C50" t="n">
         <v>15.9375</v>
@@ -1437,11 +1449,11 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>40237</v>
       </c>
       <c r="B51" t="n">
-        <v>13.36990261077881</v>
+        <v>13.36990642547607</v>
       </c>
       <c r="C51" t="n">
         <v>16.89999961853027</v>
@@ -1462,7 +1474,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>40268</v>
       </c>
       <c r="B52" t="n">
@@ -1487,11 +1499,11 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>40298</v>
       </c>
       <c r="B53" t="n">
-        <v>15.07363033294678</v>
+        <v>15.07362747192383</v>
       </c>
       <c r="C53" t="n">
         <v>18.97750091552734</v>
@@ -1512,11 +1524,11 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>40329</v>
       </c>
       <c r="B54" t="n">
-        <v>14.37266159057617</v>
+        <v>14.37266540527344</v>
       </c>
       <c r="C54" t="n">
         <v>18.09499931335449</v>
@@ -1537,11 +1549,11 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>40359</v>
       </c>
       <c r="B55" t="n">
-        <v>13.46335315704346</v>
+        <v>13.46335983276367</v>
       </c>
       <c r="C55" t="n">
         <v>16.88750076293945</v>
@@ -1562,11 +1574,11 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>40390</v>
       </c>
       <c r="B56" t="n">
-        <v>14.67714977264404</v>
+        <v>14.67715358734131</v>
       </c>
       <c r="C56" t="n">
         <v>18.40999984741211</v>
@@ -1591,11 +1603,11 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>40421</v>
       </c>
       <c r="B57" t="n">
-        <v>13.95166778564453</v>
+        <v>13.95166301727295</v>
       </c>
       <c r="C57" t="n">
         <v>17.5</v>
@@ -1620,7 +1632,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>40451</v>
       </c>
       <c r="B58" t="n">
@@ -1649,11 +1661,11 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>40482</v>
       </c>
       <c r="B59" t="n">
-        <v>16.29275131225586</v>
+        <v>16.29275512695312</v>
       </c>
       <c r="C59" t="n">
         <v>20.36000061035156</v>
@@ -1678,11 +1690,11 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>40512</v>
       </c>
       <c r="B60" t="n">
-        <v>17.23102951049805</v>
+        <v>17.23101806640625</v>
       </c>
       <c r="C60" t="n">
         <v>21.53249931335449</v>
@@ -1707,7 +1719,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>40543</v>
       </c>
       <c r="B61" t="n">
@@ -1736,11 +1748,11 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>40574</v>
       </c>
       <c r="B62" t="n">
-        <v>16.55938339233398</v>
+        <v>16.55939102172852</v>
       </c>
       <c r="C62" t="n">
         <v>20.6200008392334</v>
@@ -1765,11 +1777,11 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>40602</v>
       </c>
       <c r="B63" t="n">
-        <v>17.87442207336426</v>
+        <v>17.87442016601562</v>
       </c>
       <c r="C63" t="n">
         <v>22.25749969482422</v>
@@ -1794,11 +1806,11 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>40633</v>
       </c>
       <c r="B64" t="n">
-        <v>15.25170612335205</v>
+        <v>15.25169563293457</v>
       </c>
       <c r="C64" t="n">
         <v>18.92499923706055</v>
@@ -1823,11 +1835,11 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>40663</v>
       </c>
       <c r="B65" t="n">
-        <v>16.58547210693359</v>
+        <v>16.58547019958496</v>
       </c>
       <c r="C65" t="n">
         <v>20.57999992370605</v>
@@ -1852,11 +1864,11 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>40694</v>
       </c>
       <c r="B66" t="n">
-        <v>17.01461410522461</v>
+        <v>17.01460647583008</v>
       </c>
       <c r="C66" t="n">
         <v>21.11249923706055</v>
@@ -1881,11 +1893,11 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>40724</v>
       </c>
       <c r="B67" t="n">
-        <v>18.19744682312012</v>
+        <v>18.19744110107422</v>
       </c>
       <c r="C67" t="n">
         <v>22.4950008392334</v>
@@ -1910,11 +1922,11 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>40755</v>
       </c>
       <c r="B68" t="n">
-        <v>18.23183441162109</v>
+        <v>18.2318229675293</v>
       </c>
       <c r="C68" t="n">
         <v>22.53750038146973</v>
@@ -1939,11 +1951,11 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>40786</v>
       </c>
       <c r="B69" t="n">
-        <v>17.52399253845215</v>
+        <v>17.52398872375488</v>
       </c>
       <c r="C69" t="n">
         <v>21.66250038146973</v>
@@ -1968,7 +1980,7 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>40816</v>
       </c>
       <c r="B70" t="n">
@@ -1997,11 +2009,11 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>40847</v>
       </c>
       <c r="B71" t="n">
-        <v>19.55566787719727</v>
+        <v>19.55566024780273</v>
       </c>
       <c r="C71" t="n">
         <v>24.08749961853027</v>
@@ -2026,11 +2038,11 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>40877</v>
       </c>
       <c r="B72" t="n">
-        <v>19.52117538452148</v>
+        <v>19.52116203308105</v>
       </c>
       <c r="C72" t="n">
         <v>24.04500007629395</v>
@@ -2055,11 +2067,11 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>40908</v>
       </c>
       <c r="B73" t="n">
-        <v>19.63321685791016</v>
+        <v>19.63321495056152</v>
       </c>
       <c r="C73" t="n">
         <v>24.09250068664551</v>
@@ -2084,11 +2096,11 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="1" t="n">
+      <c r="A74" s="2" t="n">
         <v>40939</v>
       </c>
       <c r="B74" t="n">
-        <v>21.18561744689941</v>
+        <v>21.18561553955078</v>
       </c>
       <c r="C74" t="n">
         <v>25.99749946594238</v>
@@ -2113,11 +2125,11 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="1" t="n">
+      <c r="A75" s="2" t="n">
         <v>40968</v>
       </c>
       <c r="B75" t="n">
-        <v>21.98625946044922</v>
+        <v>21.98626327514648</v>
       </c>
       <c r="C75" t="n">
         <v>26.97999954223633</v>
@@ -2142,11 +2154,11 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="1" t="n">
+      <c r="A76" s="2" t="n">
         <v>40999</v>
       </c>
       <c r="B76" t="n">
-        <v>22.16614723205566</v>
+        <v>22.16615104675293</v>
       </c>
       <c r="C76" t="n">
         <v>27.11000061035156</v>
@@ -2171,11 +2183,11 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="1" t="n">
+      <c r="A77" s="2" t="n">
         <v>41029</v>
       </c>
       <c r="B77" t="n">
-        <v>22.86727714538574</v>
+        <v>22.86726951599121</v>
       </c>
       <c r="C77" t="n">
         <v>27.96750068664551</v>
@@ -2200,11 +2212,11 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="1" t="n">
+      <c r="A78" s="2" t="n">
         <v>41060</v>
       </c>
       <c r="B78" t="n">
-        <v>22.18654441833496</v>
+        <v>22.18653678894043</v>
       </c>
       <c r="C78" t="n">
         <v>27.04500007629395</v>
@@ -2229,7 +2241,7 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="1" t="n">
+      <c r="A79" s="2" t="n">
         <v>41090</v>
       </c>
       <c r="B79" t="n">
@@ -2258,11 +2270,11 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="1" t="n">
+      <c r="A80" s="2" t="n">
         <v>41121</v>
       </c>
       <c r="B80" t="n">
-        <v>19.14506721496582</v>
+        <v>19.14506530761719</v>
       </c>
       <c r="C80" t="n">
         <v>23.33749961853027</v>
@@ -2287,11 +2299,11 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="1" t="n">
+      <c r="A81" s="2" t="n">
         <v>41152</v>
       </c>
       <c r="B81" t="n">
-        <v>20.04058456420898</v>
+        <v>20.04058074951172</v>
       </c>
       <c r="C81" t="n">
         <v>24.34000015258789</v>
@@ -2316,11 +2328,11 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="1" t="n">
+      <c r="A82" s="2" t="n">
         <v>41182</v>
       </c>
       <c r="B82" t="n">
-        <v>19.53627586364746</v>
+        <v>19.53627395629883</v>
       </c>
       <c r="C82" t="n">
         <v>23.72750091552734</v>
@@ -2345,11 +2357,11 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="1" t="n">
+      <c r="A83" s="2" t="n">
         <v>41213</v>
       </c>
       <c r="B83" t="n">
-        <v>18.80965614318848</v>
+        <v>18.80965995788574</v>
       </c>
       <c r="C83" t="n">
         <v>22.84499931335449</v>
@@ -2374,11 +2386,11 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="1" t="n">
+      <c r="A84" s="2" t="n">
         <v>41243</v>
       </c>
       <c r="B84" t="n">
-        <v>20.06527900695801</v>
+        <v>20.06528663635254</v>
       </c>
       <c r="C84" t="n">
         <v>24.3700008392334</v>
@@ -2403,7 +2415,7 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="1" t="n">
+      <c r="A85" s="2" t="n">
         <v>41274</v>
       </c>
       <c r="B85" t="n">
@@ -2432,11 +2444,11 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="1" t="n">
+      <c r="A86" s="2" t="n">
         <v>41305</v>
       </c>
       <c r="B86" t="n">
-        <v>22.34738540649414</v>
+        <v>22.34738922119141</v>
       </c>
       <c r="C86" t="n">
         <v>27.02499961853027</v>
@@ -2461,11 +2473,11 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="1" t="n">
+      <c r="A87" s="2" t="n">
         <v>41333</v>
       </c>
       <c r="B87" t="n">
-        <v>22.60426712036133</v>
+        <v>22.60426330566406</v>
       </c>
       <c r="C87" t="n">
         <v>27.22999954223633</v>
@@ -2490,11 +2502,11 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="1" t="n">
+      <c r="A88" s="2" t="n">
         <v>41364</v>
       </c>
       <c r="B88" t="n">
-        <v>24.49279022216797</v>
+        <v>24.49279403686523</v>
       </c>
       <c r="C88" t="n">
         <v>29.5049991607666</v>
@@ -2519,11 +2531,11 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="1" t="n">
+      <c r="A89" s="2" t="n">
         <v>41394</v>
       </c>
       <c r="B89" t="n">
-        <v>26.39791870117188</v>
+        <v>26.39792823791504</v>
       </c>
       <c r="C89" t="n">
         <v>31.79999923706055</v>
@@ -2548,11 +2560,11 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="1" t="n">
+      <c r="A90" s="2" t="n">
         <v>41425</v>
       </c>
       <c r="B90" t="n">
-        <v>25.67839431762695</v>
+        <v>25.67839241027832</v>
       </c>
       <c r="C90" t="n">
         <v>30.82999992370605</v>
@@ -2577,11 +2589,11 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="1" t="n">
+      <c r="A91" s="2" t="n">
         <v>41455</v>
       </c>
       <c r="B91" t="n">
-        <v>26.51962661743164</v>
+        <v>26.51963233947754</v>
       </c>
       <c r="C91" t="n">
         <v>31.84000015258789</v>
@@ -2606,11 +2618,11 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="1" t="n">
+      <c r="A92" s="2" t="n">
         <v>41486</v>
       </c>
       <c r="B92" t="n">
-        <v>26.20312118530273</v>
+        <v>26.20312881469727</v>
       </c>
       <c r="C92" t="n">
         <v>31.45999908447266</v>
@@ -2635,11 +2647,11 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="1" t="n">
+      <c r="A93" s="2" t="n">
         <v>41517</v>
       </c>
       <c r="B93" t="n">
-        <v>26.24846458435059</v>
+        <v>26.24846649169922</v>
       </c>
       <c r="C93" t="n">
         <v>31.40999984741211</v>
@@ -2664,7 +2676,7 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="1" t="n">
+      <c r="A94" s="2" t="n">
         <v>41547</v>
       </c>
       <c r="B94" t="n">
@@ -2693,11 +2705,11 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="1" t="n">
+      <c r="A95" s="2" t="n">
         <v>41578</v>
       </c>
       <c r="B95" t="n">
-        <v>31.6552619934082</v>
+        <v>31.6552677154541</v>
       </c>
       <c r="C95" t="n">
         <v>37.88000106811523</v>
@@ -2722,11 +2734,11 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="1" t="n">
+      <c r="A96" s="2" t="n">
         <v>41608</v>
       </c>
       <c r="B96" t="n">
-        <v>33.06753921508789</v>
+        <v>33.06755065917969</v>
       </c>
       <c r="C96" t="n">
         <v>39.56999969482422</v>
@@ -2751,7 +2763,7 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="1" t="n">
+      <c r="A97" s="2" t="n">
         <v>41639</v>
       </c>
       <c r="B97" t="n">
@@ -2780,11 +2792,11 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="1" t="n">
+      <c r="A98" s="2" t="n">
         <v>41670</v>
       </c>
       <c r="B98" t="n">
-        <v>30.53473854064941</v>
+        <v>30.53472709655762</v>
       </c>
       <c r="C98" t="n">
         <v>36.42499923706055</v>
@@ -2809,11 +2821,11 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="1" t="n">
+      <c r="A99" s="2" t="n">
         <v>41698</v>
       </c>
       <c r="B99" t="n">
-        <v>32.91982650756836</v>
+        <v>32.91981887817383</v>
       </c>
       <c r="C99" t="n">
         <v>39.15000152587891</v>
@@ -2838,11 +2850,11 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="1" t="n">
+      <c r="A100" s="2" t="n">
         <v>41729</v>
       </c>
       <c r="B100" t="n">
-        <v>31.05310821533203</v>
+        <v>31.0531177520752</v>
       </c>
       <c r="C100" t="n">
         <v>36.93000030517578</v>
@@ -2867,11 +2879,11 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="1" t="n">
+      <c r="A101" s="2" t="n">
         <v>41759</v>
       </c>
       <c r="B101" t="n">
-        <v>30.67050743103027</v>
+        <v>30.67050361633301</v>
       </c>
       <c r="C101" t="n">
         <v>36.47499847412109</v>
@@ -2896,7 +2908,7 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="1" t="n">
+      <c r="A102" s="2" t="n">
         <v>41790</v>
       </c>
       <c r="B102" t="n">
@@ -2925,11 +2937,11 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="1" t="n">
+      <c r="A103" s="2" t="n">
         <v>41820</v>
       </c>
       <c r="B103" t="n">
-        <v>32.70742416381836</v>
+        <v>32.70743560791016</v>
       </c>
       <c r="C103" t="n">
         <v>38.77500152587891</v>
@@ -2954,11 +2966,11 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="1" t="n">
+      <c r="A104" s="2" t="n">
         <v>41851</v>
       </c>
       <c r="B104" t="n">
-        <v>32.53028869628906</v>
+        <v>32.53026962280273</v>
       </c>
       <c r="C104" t="n">
         <v>38.56499862670898</v>
@@ -2983,11 +2995,11 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="1" t="n">
+      <c r="A105" s="2" t="n">
         <v>41882</v>
       </c>
       <c r="B105" t="n">
-        <v>33.22922134399414</v>
+        <v>33.22922515869141</v>
       </c>
       <c r="C105" t="n">
         <v>39.27500152587891</v>
@@ -3012,11 +3024,11 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="1" t="n">
+      <c r="A106" s="2" t="n">
         <v>41912</v>
       </c>
       <c r="B106" t="n">
-        <v>37.73451232910156</v>
+        <v>37.73451614379883</v>
       </c>
       <c r="C106" t="n">
         <v>44.59999847412109</v>
@@ -3041,11 +3053,11 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="1" t="n">
+      <c r="A107" s="2" t="n">
         <v>41943</v>
       </c>
       <c r="B107" t="n">
-        <v>39.32935333251953</v>
+        <v>39.329345703125</v>
       </c>
       <c r="C107" t="n">
         <v>46.48500061035156</v>
@@ -3070,11 +3082,11 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="1" t="n">
+      <c r="A108" s="2" t="n">
         <v>41973</v>
       </c>
       <c r="B108" t="n">
-        <v>42.00292205810547</v>
+        <v>42.0029182434082</v>
       </c>
       <c r="C108" t="n">
         <v>49.64500045776367</v>
@@ -3099,11 +3111,11 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="1" t="n">
+      <c r="A109" s="2" t="n">
         <v>42004</v>
       </c>
       <c r="B109" t="n">
-        <v>40.79154968261719</v>
+        <v>40.79155349731445</v>
       </c>
       <c r="C109" t="n">
         <v>48.07500076293945</v>
@@ -3128,7 +3140,7 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="1" t="n">
+      <c r="A110" s="2" t="n">
         <v>42035</v>
       </c>
       <c r="B110" t="n">
@@ -3157,11 +3169,11 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="1" t="n">
+      <c r="A111" s="2" t="n">
         <v>42063</v>
       </c>
       <c r="B111" t="n">
-        <v>41.32257461547852</v>
+        <v>41.32257080078125</v>
       </c>
       <c r="C111" t="n">
         <v>48.56000137329102</v>
@@ -3186,11 +3198,11 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="1" t="n">
+      <c r="A112" s="2" t="n">
         <v>42094</v>
       </c>
       <c r="B112" t="n">
-        <v>42.6883544921875</v>
+        <v>42.68834686279297</v>
       </c>
       <c r="C112" t="n">
         <v>50.16500091552734</v>
@@ -3215,7 +3227,7 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="1" t="n">
+      <c r="A113" s="2" t="n">
         <v>42124</v>
       </c>
       <c r="B113" t="n">
@@ -3244,7 +3256,7 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="1" t="n">
+      <c r="A114" s="2" t="n">
         <v>42155</v>
       </c>
       <c r="B114" t="n">
@@ -3273,11 +3285,11 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="1" t="n">
+      <c r="A115" s="2" t="n">
         <v>42185</v>
       </c>
       <c r="B115" t="n">
-        <v>46.08577346801758</v>
+        <v>46.08578109741211</v>
       </c>
       <c r="C115" t="n">
         <v>54.0099983215332</v>
@@ -3302,11 +3314,11 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="1" t="n">
+      <c r="A116" s="2" t="n">
         <v>42216</v>
       </c>
       <c r="B116" t="n">
-        <v>49.15759658813477</v>
+        <v>49.1575927734375</v>
       </c>
       <c r="C116" t="n">
         <v>57.61000061035156</v>
@@ -3331,11 +3343,11 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="1" t="n">
+      <c r="A117" s="2" t="n">
         <v>42247</v>
       </c>
       <c r="B117" t="n">
-        <v>47.67714691162109</v>
+        <v>47.67715454101562</v>
       </c>
       <c r="C117" t="n">
         <v>55.875</v>
@@ -3360,7 +3372,7 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="1" t="n">
+      <c r="A118" s="2" t="n">
         <v>42277</v>
       </c>
       <c r="B118" t="n">
@@ -3389,11 +3401,11 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="1" t="n">
+      <c r="A119" s="2" t="n">
         <v>42308</v>
       </c>
       <c r="B119" t="n">
-        <v>56.04453277587891</v>
+        <v>56.0445442199707</v>
       </c>
       <c r="C119" t="n">
         <v>65.51499938964844</v>
@@ -3418,11 +3430,11 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="1" t="n">
+      <c r="A120" s="2" t="n">
         <v>42338</v>
       </c>
       <c r="B120" t="n">
-        <v>56.57920074462891</v>
+        <v>56.57918548583984</v>
       </c>
       <c r="C120" t="n">
         <v>66.13999938964844</v>
@@ -3447,11 +3459,11 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="1" t="n">
+      <c r="A121" s="2" t="n">
         <v>42369</v>
       </c>
       <c r="B121" t="n">
-        <v>53.59497451782227</v>
+        <v>53.5949821472168</v>
       </c>
       <c r="C121" t="n">
         <v>62.5</v>
@@ -3476,11 +3488,11 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="1" t="n">
+      <c r="A122" s="2" t="n">
         <v>42400</v>
       </c>
       <c r="B122" t="n">
-        <v>53.17478561401367</v>
+        <v>53.1747932434082</v>
       </c>
       <c r="C122" t="n">
         <v>62.0099983215332</v>
@@ -3505,11 +3517,11 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="1" t="n">
+      <c r="A123" s="2" t="n">
         <v>42429</v>
       </c>
       <c r="B123" t="n">
-        <v>52.81462860107422</v>
+        <v>52.81463241577148</v>
       </c>
       <c r="C123" t="n">
         <v>61.59000015258789</v>
@@ -3534,11 +3546,11 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="1" t="n">
+      <c r="A124" s="2" t="n">
         <v>42460</v>
       </c>
       <c r="B124" t="n">
-        <v>52.84763717651367</v>
+        <v>52.84762954711914</v>
       </c>
       <c r="C124" t="n">
         <v>61.47000122070312</v>
@@ -3563,7 +3575,7 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="1" t="n">
+      <c r="A125" s="2" t="n">
         <v>42490</v>
       </c>
       <c r="B125" t="n">
@@ -3592,11 +3604,11 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="1" t="n">
+      <c r="A126" s="2" t="n">
         <v>42521</v>
       </c>
       <c r="B126" t="n">
-        <v>47.47433090209961</v>
+        <v>47.47432708740234</v>
       </c>
       <c r="C126" t="n">
         <v>55.22000122070312</v>
@@ -3621,11 +3633,11 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="1" t="n">
+      <c r="A127" s="2" t="n">
         <v>42551</v>
       </c>
       <c r="B127" t="n">
-        <v>47.59574890136719</v>
+        <v>47.59575653076172</v>
       </c>
       <c r="C127" t="n">
         <v>55.20000076293945</v>
@@ -3650,11 +3662,11 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="1" t="n">
+      <c r="A128" s="2" t="n">
         <v>42582</v>
       </c>
       <c r="B128" t="n">
-        <v>47.85442733764648</v>
+        <v>47.85443115234375</v>
       </c>
       <c r="C128" t="n">
         <v>55.5</v>
@@ -3679,11 +3691,11 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="1" t="n">
+      <c r="A129" s="2" t="n">
         <v>42613</v>
       </c>
       <c r="B129" t="n">
-        <v>49.69963455200195</v>
+        <v>49.69962692260742</v>
       </c>
       <c r="C129" t="n">
         <v>57.63999938964844</v>
@@ -3708,11 +3720,11 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="1" t="n">
+      <c r="A130" s="2" t="n">
         <v>42643</v>
       </c>
       <c r="B130" t="n">
-        <v>45.52341079711914</v>
+        <v>45.52341461181641</v>
       </c>
       <c r="C130" t="n">
         <v>52.65000152587891</v>
@@ -3737,11 +3749,11 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="1" t="n">
+      <c r="A131" s="2" t="n">
         <v>42674</v>
       </c>
       <c r="B131" t="n">
-        <v>43.38774871826172</v>
+        <v>43.38775634765625</v>
       </c>
       <c r="C131" t="n">
         <v>50.18000030517578</v>
@@ -3766,11 +3778,11 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="1" t="n">
+      <c r="A132" s="2" t="n">
         <v>42704</v>
       </c>
       <c r="B132" t="n">
-        <v>43.29262924194336</v>
+        <v>43.29264068603516</v>
       </c>
       <c r="C132" t="n">
         <v>50.06999969482422</v>
@@ -3795,11 +3807,11 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="1" t="n">
+      <c r="A133" s="2" t="n">
         <v>42735</v>
       </c>
       <c r="B133" t="n">
-        <v>44.10833358764648</v>
+        <v>44.10834884643555</v>
       </c>
       <c r="C133" t="n">
         <v>50.83000183105469</v>
@@ -3824,11 +3836,11 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="1" t="n">
+      <c r="A134" s="2" t="n">
         <v>42766</v>
       </c>
       <c r="B134" t="n">
-        <v>45.90459060668945</v>
+        <v>45.90459823608398</v>
       </c>
       <c r="C134" t="n">
         <v>52.90000152587891</v>
@@ -3853,11 +3865,11 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="1" t="n">
+      <c r="A135" s="2" t="n">
         <v>42794</v>
       </c>
       <c r="B135" t="n">
-        <v>49.60125350952148</v>
+        <v>49.60125732421875</v>
       </c>
       <c r="C135" t="n">
         <v>57.15999984741211</v>
@@ -3882,11 +3894,11 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="1" t="n">
+      <c r="A136" s="2" t="n">
         <v>42825</v>
       </c>
       <c r="B136" t="n">
-        <v>48.51105880737305</v>
+        <v>48.51104736328125</v>
       </c>
       <c r="C136" t="n">
         <v>55.72999954223633</v>
@@ -3911,7 +3923,7 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="1" t="n">
+      <c r="A137" s="2" t="n">
         <v>42855</v>
       </c>
       <c r="B137" t="n">
@@ -3940,11 +3952,11 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="1" t="n">
+      <c r="A138" s="2" t="n">
         <v>42886</v>
       </c>
       <c r="B138" t="n">
-        <v>46.1259765625</v>
+        <v>46.1259651184082</v>
       </c>
       <c r="C138" t="n">
         <v>52.9900016784668</v>
@@ -3969,11 +3981,11 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="1" t="n">
+      <c r="A139" s="2" t="n">
         <v>42916</v>
       </c>
       <c r="B139" t="n">
-        <v>51.53251647949219</v>
+        <v>51.53252792358398</v>
       </c>
       <c r="C139" t="n">
         <v>59</v>
@@ -3998,11 +4010,11 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="1" t="n">
+      <c r="A140" s="2" t="n">
         <v>42947</v>
       </c>
       <c r="B140" t="n">
-        <v>51.5761833190918</v>
+        <v>51.57619857788086</v>
       </c>
       <c r="C140" t="n">
         <v>59.04999923706055</v>
@@ -4027,11 +4039,11 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="1" t="n">
+      <c r="A141" s="2" t="n">
         <v>42978</v>
       </c>
       <c r="B141" t="n">
-        <v>46.28448104858398</v>
+        <v>46.28446578979492</v>
       </c>
       <c r="C141" t="n">
         <v>52.81000137329102</v>
@@ -4056,11 +4068,11 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="1" t="n">
+      <c r="A142" s="2" t="n">
         <v>43008</v>
       </c>
       <c r="B142" t="n">
-        <v>45.44308853149414</v>
+        <v>45.4431037902832</v>
       </c>
       <c r="C142" t="n">
         <v>51.84999847412109</v>
@@ -4085,11 +4097,11 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="1" t="n">
+      <c r="A143" s="2" t="n">
         <v>43039</v>
       </c>
       <c r="B143" t="n">
-        <v>48.19510650634766</v>
+        <v>48.19509887695312</v>
       </c>
       <c r="C143" t="n">
         <v>54.9900016784668</v>
@@ -4114,11 +4126,11 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="1" t="n">
+      <c r="A144" s="2" t="n">
         <v>43069</v>
       </c>
       <c r="B144" t="n">
-        <v>52.95413970947266</v>
+        <v>52.95413589477539</v>
       </c>
       <c r="C144" t="n">
         <v>60.41999816894531</v>
@@ -4143,11 +4155,11 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="1" t="n">
+      <c r="A145" s="2" t="n">
         <v>43100</v>
       </c>
       <c r="B145" t="n">
-        <v>55.00300979614258</v>
+        <v>55.00301361083984</v>
       </c>
       <c r="C145" t="n">
         <v>62.54999923706055</v>
@@ -4172,7 +4184,7 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="1" t="n">
+      <c r="A146" s="2" t="n">
         <v>43131</v>
       </c>
       <c r="B146" t="n">
@@ -4201,11 +4213,11 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="1" t="n">
+      <c r="A147" s="2" t="n">
         <v>43159</v>
       </c>
       <c r="B147" t="n">
-        <v>58.94247817993164</v>
+        <v>58.94247436523438</v>
       </c>
       <c r="C147" t="n">
         <v>67.02999877929688</v>
@@ -4230,11 +4242,11 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="1" t="n">
+      <c r="A148" s="2" t="n">
         <v>43190</v>
       </c>
       <c r="B148" t="n">
-        <v>58.60037612915039</v>
+        <v>58.60038375854492</v>
       </c>
       <c r="C148" t="n">
         <v>66.44000244140625</v>
@@ -4259,11 +4271,11 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="1" t="n">
+      <c r="A149" s="2" t="n">
         <v>43220</v>
       </c>
       <c r="B149" t="n">
-        <v>60.32030868530273</v>
+        <v>60.32028961181641</v>
       </c>
       <c r="C149" t="n">
         <v>68.38999938964844</v>
@@ -4288,11 +4300,11 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="1" t="n">
+      <c r="A150" s="2" t="n">
         <v>43251</v>
       </c>
       <c r="B150" t="n">
-        <v>63.32791900634766</v>
+        <v>63.32794189453125</v>
       </c>
       <c r="C150" t="n">
         <v>71.80000305175781</v>
@@ -4317,11 +4329,11 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="1" t="n">
+      <c r="A151" s="2" t="n">
         <v>43281</v>
       </c>
       <c r="B151" t="n">
-        <v>70.47444152832031</v>
+        <v>70.47442626953125</v>
       </c>
       <c r="C151" t="n">
         <v>79.68000030517578</v>
@@ -4346,11 +4358,11 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="1" t="n">
+      <c r="A152" s="2" t="n">
         <v>43312</v>
       </c>
       <c r="B152" t="n">
-        <v>68.02445220947266</v>
+        <v>68.02445983886719</v>
       </c>
       <c r="C152" t="n">
         <v>76.91000366210938</v>
@@ -4375,11 +4387,11 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="1" t="n">
+      <c r="A153" s="2" t="n">
         <v>43343</v>
       </c>
       <c r="B153" t="n">
-        <v>72.88234710693359</v>
+        <v>72.88235473632812</v>
       </c>
       <c r="C153" t="n">
         <v>82.19999694824219</v>
@@ -4404,11 +4416,11 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="1" t="n">
+      <c r="A154" s="2" t="n">
         <v>43373</v>
       </c>
       <c r="B154" t="n">
-        <v>75.11671447753906</v>
+        <v>75.11672210693359</v>
       </c>
       <c r="C154" t="n">
         <v>84.72000122070312</v>
@@ -4433,7 +4445,7 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="1" t="n">
+      <c r="A155" s="2" t="n">
         <v>43404</v>
       </c>
       <c r="B155" t="n">
@@ -4462,11 +4474,11 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="1" t="n">
+      <c r="A156" s="2" t="n">
         <v>43434</v>
       </c>
       <c r="B156" t="n">
-        <v>66.8026123046875</v>
+        <v>66.80258178710938</v>
       </c>
       <c r="C156" t="n">
         <v>75.12000274658203</v>
@@ -4491,11 +4503,11 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="1" t="n">
+      <c r="A157" s="2" t="n">
         <v>43465</v>
       </c>
       <c r="B157" t="n">
-        <v>65.93108367919922</v>
+        <v>65.93111419677734</v>
       </c>
       <c r="C157" t="n">
         <v>74.13999938964844</v>
@@ -4520,11 +4532,11 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="1" t="n">
+      <c r="A158" s="2" t="n">
         <v>43496</v>
       </c>
       <c r="B158" t="n">
-        <v>72.81410217285156</v>
+        <v>72.81410980224609</v>
       </c>
       <c r="C158" t="n">
         <v>81.87999725341797</v>
@@ -4549,11 +4561,11 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="1" t="n">
+      <c r="A159" s="2" t="n">
         <v>43524</v>
       </c>
       <c r="B159" t="n">
-        <v>76.23783111572266</v>
+        <v>76.23785400390625</v>
       </c>
       <c r="C159" t="n">
         <v>85.73000335693359</v>
@@ -4578,11 +4590,11 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="1" t="n">
+      <c r="A160" s="2" t="n">
         <v>43555</v>
       </c>
       <c r="B160" t="n">
-        <v>75.07878875732422</v>
+        <v>75.07880401611328</v>
       </c>
       <c r="C160" t="n">
         <v>84.20999908447266</v>
@@ -4607,7 +4619,7 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="1" t="n">
+      <c r="A161" s="2" t="n">
         <v>43585</v>
       </c>
       <c r="B161" t="n">
@@ -4636,11 +4648,11 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="1" t="n">
+      <c r="A162" s="2" t="n">
         <v>43616</v>
       </c>
       <c r="B162" t="n">
-        <v>68.96686553955078</v>
+        <v>68.96685791015625</v>
       </c>
       <c r="C162" t="n">
         <v>77.13999938964844</v>
@@ -4665,11 +4677,11 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="1" t="n">
+      <c r="A163" s="2" t="n">
         <v>43646</v>
       </c>
       <c r="B163" t="n">
-        <v>75.05532073974609</v>
+        <v>75.05531311035156</v>
       </c>
       <c r="C163" t="n">
         <v>83.94999694824219</v>
@@ -4694,7 +4706,7 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="1" t="n">
+      <c r="A164" s="2" t="n">
         <v>43677</v>
       </c>
       <c r="B164" t="n">
@@ -4723,11 +4735,11 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="1" t="n">
+      <c r="A165" s="2" t="n">
         <v>43708</v>
       </c>
       <c r="B165" t="n">
-        <v>75.74223327636719</v>
+        <v>75.74222564697266</v>
       </c>
       <c r="C165" t="n">
         <v>84.5</v>
@@ -4752,11 +4764,11 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="1" t="n">
+      <c r="A166" s="2" t="n">
         <v>43738</v>
       </c>
       <c r="B166" t="n">
-        <v>84.18589019775391</v>
+        <v>84.18593597412109</v>
       </c>
       <c r="C166" t="n">
         <v>93.91999816894531</v>
@@ -4781,11 +4793,11 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="1" t="n">
+      <c r="A167" s="2" t="n">
         <v>43769</v>
       </c>
       <c r="B167" t="n">
-        <v>80.26882934570312</v>
+        <v>80.26883697509766</v>
       </c>
       <c r="C167" t="n">
         <v>89.55000305175781</v>
@@ -4810,11 +4822,11 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="1" t="n">
+      <c r="A168" s="2" t="n">
         <v>43799</v>
       </c>
       <c r="B168" t="n">
-        <v>84.01913452148438</v>
+        <v>84.01912689208984</v>
       </c>
       <c r="C168" t="n">
         <v>93.48999786376953</v>
@@ -4839,11 +4851,11 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="1" t="n">
+      <c r="A169" s="2" t="n">
         <v>43830</v>
       </c>
       <c r="B169" t="n">
-        <v>91.04695892333984</v>
+        <v>91.04695129394531</v>
       </c>
       <c r="C169" t="n">
         <v>101.3099975585938</v>
@@ -4868,11 +4880,11 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="1" t="n">
+      <c r="A170" s="2" t="n">
         <v>43861</v>
       </c>
       <c r="B170" t="n">
-        <v>86.54447174072266</v>
+        <v>86.54448699951172</v>
       </c>
       <c r="C170" t="n">
         <v>96.30000305175781</v>
@@ -4897,11 +4909,11 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="1" t="n">
+      <c r="A171" s="2" t="n">
         <v>43890</v>
       </c>
       <c r="B171" t="n">
-        <v>80.54836273193359</v>
+        <v>80.54835510253906</v>
       </c>
       <c r="C171" t="n">
         <v>89.37999725341797</v>
@@ -4926,11 +4938,11 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="1" t="n">
+      <c r="A172" s="2" t="n">
         <v>43921</v>
       </c>
       <c r="B172" t="n">
-        <v>74.564453125</v>
+        <v>74.56444549560547</v>
       </c>
       <c r="C172" t="n">
         <v>82.73999786376953</v>
@@ -4955,11 +4967,11 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="1" t="n">
+      <c r="A173" s="2" t="n">
         <v>43951</v>
       </c>
       <c r="B173" t="n">
-        <v>78.56572723388672</v>
+        <v>78.56573486328125</v>
       </c>
       <c r="C173" t="n">
         <v>87.18000030517578</v>
@@ -4984,11 +4996,11 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="1" t="n">
+      <c r="A174" s="2" t="n">
         <v>43982</v>
       </c>
       <c r="B174" t="n">
-        <v>89.06092834472656</v>
+        <v>89.06092071533203</v>
       </c>
       <c r="C174" t="n">
         <v>98.58000183105469</v>
@@ -5013,11 +5025,11 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="1" t="n">
+      <c r="A175" s="2" t="n">
         <v>44012</v>
       </c>
       <c r="B175" t="n">
-        <v>88.58210754394531</v>
+        <v>88.58209228515625</v>
       </c>
       <c r="C175" t="n">
         <v>98.05000305175781</v>
@@ -5042,11 +5054,11 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="1" t="n">
+      <c r="A176" s="2" t="n">
         <v>44043</v>
       </c>
       <c r="B176" t="n">
-        <v>88.18458557128906</v>
+        <v>88.18457794189453</v>
       </c>
       <c r="C176" t="n">
         <v>97.61000061035156</v>
@@ -5071,11 +5083,11 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="1" t="n">
+      <c r="A177" s="2" t="n">
         <v>44074</v>
       </c>
       <c r="B177" t="n">
-        <v>101.3096008300781</v>
+        <v>101.3096084594727</v>
       </c>
       <c r="C177" t="n">
         <v>111.8899993896484</v>
@@ -5100,11 +5112,11 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="1" t="n">
+      <c r="A178" s="2" t="n">
         <v>44104</v>
       </c>
       <c r="B178" t="n">
-        <v>113.6688461303711</v>
+        <v>113.6688613891602</v>
       </c>
       <c r="C178" t="n">
         <v>125.5400009155273</v>
@@ -5129,7 +5141,7 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="1" t="n">
+      <c r="A179" s="2" t="n">
         <v>44135</v>
       </c>
       <c r="B179" t="n">
@@ -5158,11 +5170,11 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="1" t="n">
+      <c r="A180" s="2" t="n">
         <v>44165</v>
       </c>
       <c r="B180" t="n">
-        <v>121.9626388549805</v>
+        <v>121.9626922607422</v>
       </c>
       <c r="C180" t="n">
         <v>134.6999969482422</v>
@@ -5187,11 +5199,11 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="1" t="n">
+      <c r="A181" s="2" t="n">
         <v>44196</v>
       </c>
       <c r="B181" t="n">
-        <v>128.3502197265625</v>
+        <v>128.3502349853516</v>
       </c>
       <c r="C181" t="n">
         <v>141.4700012207031</v>
@@ -5216,11 +5228,11 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="1" t="n">
+      <c r="A182" s="2" t="n">
         <v>44227</v>
       </c>
       <c r="B182" t="n">
-        <v>121.2009658813477</v>
+        <v>121.2009887695312</v>
       </c>
       <c r="C182" t="n">
         <v>133.5899963378906</v>
@@ -5245,11 +5257,11 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="1" t="n">
+      <c r="A183" s="2" t="n">
         <v>44255</v>
       </c>
       <c r="B183" t="n">
-        <v>122.5292510986328</v>
+        <v>122.5292205810547</v>
       </c>
       <c r="C183" t="n">
         <v>134.7799987792969</v>
@@ -5274,11 +5286,11 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="1" t="n">
+      <c r="A184" s="2" t="n">
         <v>44286</v>
       </c>
       <c r="B184" t="n">
-        <v>120.8110427856445</v>
+        <v>120.8110504150391</v>
       </c>
       <c r="C184" t="n">
         <v>132.8899993896484</v>
@@ -5303,11 +5315,11 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="1" t="n">
+      <c r="A185" s="2" t="n">
         <v>44316</v>
       </c>
       <c r="B185" t="n">
-        <v>120.5656051635742</v>
+        <v>120.5655975341797</v>
       </c>
       <c r="C185" t="n">
         <v>132.6199951171875</v>
@@ -5332,11 +5344,11 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="1" t="n">
+      <c r="A186" s="2" t="n">
         <v>44347</v>
       </c>
       <c r="B186" t="n">
-        <v>124.3068695068359</v>
+        <v>124.3068771362305</v>
       </c>
       <c r="C186" t="n">
         <v>136.4600067138672</v>
@@ -5361,11 +5373,11 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="1" t="n">
+      <c r="A187" s="2" t="n">
         <v>44377</v>
       </c>
       <c r="B187" t="n">
-        <v>140.7311401367188</v>
+        <v>140.7310943603516</v>
       </c>
       <c r="C187" t="n">
         <v>154.4900054931641</v>
@@ -5390,7 +5402,7 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="1" t="n">
+      <c r="A188" s="2" t="n">
         <v>44408</v>
       </c>
       <c r="B188" t="n">
@@ -5419,11 +5431,11 @@
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="1" t="n">
+      <c r="A189" s="2" t="n">
         <v>44439</v>
       </c>
       <c r="B189" t="n">
-        <v>150.3158874511719</v>
+        <v>150.3159027099609</v>
       </c>
       <c r="C189" t="n">
         <v>164.7400054931641</v>
@@ -5448,11 +5460,11 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="1" t="n">
+      <c r="A190" s="2" t="n">
         <v>44469</v>
       </c>
       <c r="B190" t="n">
-        <v>132.5141143798828</v>
+        <v>132.5141296386719</v>
       </c>
       <c r="C190" t="n">
         <v>145.2299957275391</v>
@@ -5477,11 +5489,11 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="1" t="n">
+      <c r="A191" s="2" t="n">
         <v>44500</v>
       </c>
       <c r="B191" t="n">
-        <v>152.6426086425781</v>
+        <v>152.6425933837891</v>
       </c>
       <c r="C191" t="n">
         <v>167.2899932861328</v>
@@ -5506,11 +5518,11 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="1" t="n">
+      <c r="A192" s="2" t="n">
         <v>44530</v>
       </c>
       <c r="B192" t="n">
-        <v>154.4218597412109</v>
+        <v>154.4219055175781</v>
       </c>
       <c r="C192" t="n">
         <v>169.2400054931641</v>
@@ -5535,11 +5547,11 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="1" t="n">
+      <c r="A193" s="2" t="n">
         <v>44561</v>
       </c>
       <c r="B193" t="n">
-        <v>152.3502197265625</v>
+        <v>152.3502655029297</v>
       </c>
       <c r="C193" t="n">
         <v>166.6699981689453</v>
@@ -5564,11 +5576,11 @@
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="1" t="n">
+      <c r="A194" s="2" t="n">
         <v>44592</v>
       </c>
       <c r="B194" t="n">
-        <v>135.3482818603516</v>
+        <v>135.3482971191406</v>
       </c>
       <c r="C194" t="n">
         <v>148.0700073242188</v>
@@ -5593,11 +5605,11 @@
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="1" t="n">
+      <c r="A195" s="2" t="n">
         <v>44620</v>
       </c>
       <c r="B195" t="n">
-        <v>124.8180694580078</v>
+        <v>124.8180465698242</v>
       </c>
       <c r="C195" t="n">
         <v>136.5500030517578</v>
@@ -5622,11 +5634,11 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="1" t="n">
+      <c r="A196" s="2" t="n">
         <v>44651</v>
       </c>
       <c r="B196" t="n">
-        <v>123.2796936035156</v>
+        <v>123.279670715332</v>
       </c>
       <c r="C196" t="n">
         <v>134.5599975585938</v>
@@ -5651,7 +5663,7 @@
       </c>
     </row>
     <row r="197">
-      <c r="A197" s="1" t="n">
+      <c r="A197" s="2" t="n">
         <v>44681</v>
       </c>
       <c r="B197" t="n">
@@ -5680,7 +5692,7 @@
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="1" t="n">
+      <c r="A198" s="2" t="n">
         <v>44712</v>
       </c>
       <c r="B198" t="n">
@@ -5709,11 +5721,11 @@
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="1" t="n">
+      <c r="A199" s="2" t="n">
         <v>44742</v>
       </c>
       <c r="B199" t="n">
-        <v>93.86444854736328</v>
+        <v>93.86444091796875</v>
       </c>
       <c r="C199" t="n">
         <v>102.1999969482422</v>
@@ -5738,11 +5750,11 @@
       </c>
     </row>
     <row r="200">
-      <c r="A200" s="1" t="n">
+      <c r="A200" s="2" t="n">
         <v>44773</v>
       </c>
       <c r="B200" t="n">
-        <v>105.5469970703125</v>
+        <v>105.547004699707</v>
       </c>
       <c r="C200" t="n">
         <v>114.9199981689453</v>
@@ -5767,11 +5779,11 @@
       </c>
     </row>
     <row r="201">
-      <c r="A201" s="1" t="n">
+      <c r="A201" s="2" t="n">
         <v>44804</v>
       </c>
       <c r="B201" t="n">
-        <v>97.76780700683594</v>
+        <v>97.76781463623047</v>
       </c>
       <c r="C201" t="n">
         <v>106.4499969482422</v>
@@ -5796,11 +5808,11 @@
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="1" t="n">
+      <c r="A202" s="2" t="n">
         <v>44834</v>
       </c>
       <c r="B202" t="n">
-        <v>76.55992889404297</v>
+        <v>76.55992126464844</v>
       </c>
       <c r="C202" t="n">
         <v>83.12000274658203</v>
@@ -5825,11 +5837,11 @@
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="1" t="n">
+      <c r="A203" s="2" t="n">
         <v>44865</v>
       </c>
       <c r="B203" t="n">
-        <v>85.36541748046875</v>
+        <v>85.36540222167969</v>
       </c>
       <c r="C203" t="n">
         <v>92.68000030517578</v>
@@ -5854,11 +5866,11 @@
       </c>
     </row>
     <row r="204">
-      <c r="A204" s="1" t="n">
+      <c r="A204" s="2" t="n">
         <v>44895</v>
       </c>
       <c r="B204" t="n">
-        <v>101.0329360961914</v>
+        <v>101.0329284667969</v>
       </c>
       <c r="C204" t="n">
         <v>109.6900024414062</v>
@@ -5883,11 +5895,11 @@
       </c>
     </row>
     <row r="205">
-      <c r="A205" s="1" t="n">
+      <c r="A205" s="2" t="n">
         <v>44926</v>
       </c>
       <c r="B205" t="n">
-        <v>108.1060180664062</v>
+        <v>108.1060104370117</v>
       </c>
       <c r="C205" t="n">
         <v>117.0100021362305</v>
@@ -5912,11 +5924,11 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="1" t="n">
+      <c r="A206" s="2" t="n">
         <v>44957</v>
       </c>
       <c r="B206" t="n">
-        <v>117.6407089233398</v>
+        <v>117.6407012939453</v>
       </c>
       <c r="C206" t="n">
         <v>127.3300018310547</v>
@@ -5941,11 +5953,11 @@
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="1" t="n">
+      <c r="A207" s="2" t="n">
         <v>44985</v>
       </c>
       <c r="B207" t="n">
-        <v>109.7505569458008</v>
+        <v>109.7505493164062</v>
       </c>
       <c r="C207" t="n">
         <v>118.7900009155273</v>
@@ -5970,11 +5982,11 @@
       </c>
     </row>
     <row r="208">
-      <c r="A208" s="1" t="n">
+      <c r="A208" s="2" t="n">
         <v>45016</v>
       </c>
       <c r="B208" t="n">
-        <v>113.6306762695312</v>
+        <v>113.6306610107422</v>
       </c>
       <c r="C208" t="n">
         <v>122.6399993896484</v>
@@ -5999,11 +6011,11 @@
       </c>
     </row>
     <row r="209">
-      <c r="A209" s="1" t="n">
+      <c r="A209" s="2" t="n">
         <v>45046</v>
       </c>
       <c r="B209" t="n">
-        <v>117.4109497070312</v>
+        <v>117.4109573364258</v>
       </c>
       <c r="C209" t="n">
         <v>126.7200012207031</v>
@@ -6028,11 +6040,11 @@
       </c>
     </row>
     <row r="210">
-      <c r="A210" s="1" t="n">
+      <c r="A210" s="2" t="n">
         <v>45077</v>
       </c>
       <c r="B210" t="n">
-        <v>97.52743530273438</v>
+        <v>97.52744293212891</v>
       </c>
       <c r="C210" t="n">
         <v>105.2600021362305</v>
@@ -6057,11 +6069,11 @@
       </c>
     </row>
     <row r="211">
-      <c r="A211" s="1" t="n">
+      <c r="A211" s="2" t="n">
         <v>45107</v>
       </c>
       <c r="B211" t="n">
-        <v>102.5986557006836</v>
+        <v>102.5986862182617</v>
       </c>
       <c r="C211" t="n">
         <v>110.370002746582</v>
@@ -6086,11 +6098,11 @@
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="1" t="n">
+      <c r="A212" s="2" t="n">
         <v>45138</v>
       </c>
       <c r="B212" t="n">
-        <v>102.6172409057617</v>
+        <v>102.6172485351562</v>
       </c>
       <c r="C212" t="n">
         <v>110.3899993896484</v>
@@ -6115,11 +6127,11 @@
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="1" t="n">
+      <c r="A213" s="2" t="n">
         <v>45169</v>
       </c>
       <c r="B213" t="n">
-        <v>94.54841613769531</v>
+        <v>94.54842376708984</v>
       </c>
       <c r="C213" t="n">
         <v>101.7099990844727</v>
@@ -6144,11 +6156,11 @@
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="1" t="n">
+      <c r="A214" s="2" t="n">
         <v>45199</v>
       </c>
       <c r="B214" t="n">
-        <v>89.18537139892578</v>
+        <v>89.18537902832031</v>
       </c>
       <c r="C214" t="n">
         <v>95.62000274658203</v>
@@ -6173,11 +6185,11 @@
       </c>
     </row>
     <row r="215">
-      <c r="A215" s="1" t="n">
+      <c r="A215" s="2" t="n">
         <v>45230</v>
       </c>
       <c r="B215" t="n">
-        <v>95.85421752929688</v>
+        <v>95.85423278808594</v>
       </c>
       <c r="C215" t="n">
         <v>102.7699966430664</v>
@@ -6202,11 +6214,11 @@
       </c>
     </row>
     <row r="216">
-      <c r="A216" s="1" t="n">
+      <c r="A216" s="2" t="n">
         <v>45260</v>
       </c>
       <c r="B216" t="n">
-        <v>102.8495101928711</v>
+        <v>102.8495178222656</v>
       </c>
       <c r="C216" t="n">
         <v>110.2699966430664</v>
@@ -6231,11 +6243,11 @@
       </c>
     </row>
     <row r="217">
-      <c r="A217" s="1" t="n">
+      <c r="A217" s="2" t="n">
         <v>45291</v>
       </c>
       <c r="B217" t="n">
-        <v>101.6048431396484</v>
+        <v>101.6048355102539</v>
       </c>
       <c r="C217" t="n">
         <v>108.5699996948242</v>
@@ -6260,11 +6272,11 @@
       </c>
     </row>
     <row r="218">
-      <c r="A218" s="1" t="n">
+      <c r="A218" s="2" t="n">
         <v>45322</v>
       </c>
       <c r="B218" t="n">
-        <v>95.01648712158203</v>
+        <v>95.01649475097656</v>
       </c>
       <c r="C218" t="n">
         <v>101.5299987792969</v>
@@ -6289,7 +6301,7 @@
       </c>
     </row>
     <row r="219">
-      <c r="A219" s="1" t="n">
+      <c r="A219" s="2" t="n">
         <v>45351</v>
       </c>
       <c r="B219" t="n">
@@ -6318,11 +6330,11 @@
       </c>
     </row>
     <row r="220">
-      <c r="A220" s="1" t="n">
+      <c r="A220" s="2" t="n">
         <v>45382</v>
       </c>
       <c r="B220" t="n">
-        <v>88.26507568359375</v>
+        <v>88.26508331298828</v>
       </c>
       <c r="C220" t="n">
         <v>93.98000335693359</v>
@@ -6347,7 +6359,7 @@
       </c>
     </row>
     <row r="221">
-      <c r="A221" s="1" t="n">
+      <c r="A221" s="2" t="n">
         <v>45412</v>
       </c>
       <c r="B221" t="n">
@@ -6376,11 +6388,11 @@
       </c>
     </row>
     <row r="222">
-      <c r="A222" s="1" t="n">
+      <c r="A222" s="2" t="n">
         <v>45443</v>
       </c>
       <c r="B222" t="n">
-        <v>89.27000427246094</v>
+        <v>89.27001190185547</v>
       </c>
       <c r="C222" t="n">
         <v>95.05000305175781</v>
@@ -6405,11 +6417,11 @@
       </c>
     </row>
     <row r="223">
-      <c r="A223" s="1" t="n">
+      <c r="A223" s="2" t="n">
         <v>45473</v>
       </c>
       <c r="B223" t="n">
-        <v>71.06337738037109</v>
+        <v>71.06336975097656</v>
       </c>
       <c r="C223" t="n">
         <v>75.37000274658203</v>
@@ -6434,7 +6446,7 @@
       </c>
     </row>
     <row r="224">
-      <c r="A224" s="1" t="n">
+      <c r="A224" s="2" t="n">
         <v>45504</v>
       </c>
       <c r="B224" t="n">
@@ -6463,11 +6475,11 @@
       </c>
     </row>
     <row r="225">
-      <c r="A225" s="1" t="n">
+      <c r="A225" s="2" t="n">
         <v>45535</v>
       </c>
       <c r="B225" t="n">
-        <v>78.55912017822266</v>
+        <v>78.55910491943359</v>
       </c>
       <c r="C225" t="n">
         <v>83.31999969482422</v>
@@ -6492,11 +6504,11 @@
       </c>
     </row>
     <row r="226">
-      <c r="A226" s="1" t="n">
+      <c r="A226" s="2" t="n">
         <v>45565</v>
       </c>
       <c r="B226" t="n">
-        <v>83.72061920166016</v>
+        <v>83.72062683105469</v>
       </c>
       <c r="C226" t="n">
         <v>88.40000152587891</v>
@@ -6521,11 +6533,11 @@
       </c>
     </row>
     <row r="227">
-      <c r="A227" s="1" t="n">
+      <c r="A227" s="2" t="n">
         <v>45596</v>
       </c>
       <c r="B227" t="n">
-        <v>73.04718017578125</v>
+        <v>73.04718780517578</v>
       </c>
       <c r="C227" t="n">
         <v>77.12999725341797</v>
@@ -6550,7 +6562,7 @@
       </c>
     </row>
     <row r="228">
-      <c r="A228" s="1" t="n">
+      <c r="A228" s="2" t="n">
         <v>45626</v>
       </c>
       <c r="B228" t="n">
@@ -6579,7 +6591,7 @@
       </c>
     </row>
     <row r="229">
-      <c r="A229" s="1" t="n">
+      <c r="A229" s="2" t="n">
         <v>45657</v>
       </c>
       <c r="B229" t="n">
@@ -6608,7 +6620,7 @@
       </c>
     </row>
     <row r="230">
-      <c r="A230" s="1" t="n">
+      <c r="A230" s="2" t="n">
         <v>45688</v>
       </c>
       <c r="B230" t="n">
@@ -6637,7 +6649,7 @@
       </c>
     </row>
     <row r="231">
-      <c r="A231" s="1" t="n">
+      <c r="A231" s="2" t="n">
         <v>45716</v>
       </c>
       <c r="B231" t="n">
@@ -6666,11 +6678,11 @@
       </c>
     </row>
     <row r="232">
-      <c r="A232" s="1" t="n">
+      <c r="A232" s="2" t="n">
         <v>45747</v>
       </c>
       <c r="B232" t="n">
-        <v>60.73242950439453</v>
+        <v>60.7324333190918</v>
       </c>
       <c r="C232" t="n">
         <v>63.47999954223633</v>
@@ -6695,7 +6707,7 @@
       </c>
     </row>
     <row r="233">
-      <c r="A233" s="1" t="n">
+      <c r="A233" s="2" t="n">
         <v>45777</v>
       </c>
       <c r="B233" t="n">
@@ -6724,11 +6736,11 @@
       </c>
     </row>
     <row r="234">
-      <c r="A234" s="1" t="n">
+      <c r="A234" s="2" t="n">
         <v>45808</v>
       </c>
       <c r="B234" t="n">
-        <v>57.96751403808594</v>
+        <v>57.96752166748047</v>
       </c>
       <c r="C234" t="n">
         <v>60.59000015258789</v>
@@ -6753,11 +6765,11 @@
       </c>
     </row>
     <row r="235">
-      <c r="A235" s="1" t="n">
+      <c r="A235" s="2" t="n">
         <v>45838</v>
       </c>
       <c r="B235" t="n">
-        <v>68.41688537597656</v>
+        <v>68.41689300537109</v>
       </c>
       <c r="C235" t="n">
         <v>71.04000091552734</v>
@@ -6782,11 +6794,11 @@
       </c>
     </row>
     <row r="236">
-      <c r="A236" s="1" t="n">
+      <c r="A236" s="2" t="n">
         <v>45869</v>
       </c>
       <c r="B236" t="n">
-        <v>71.93212127685547</v>
+        <v>71.93211364746094</v>
       </c>
       <c r="C236" t="n">
         <v>74.69000244140625</v>
@@ -6811,11 +6823,11 @@
       </c>
     </row>
     <row r="237">
-      <c r="A237" s="1" t="n">
+      <c r="A237" s="2" t="n">
         <v>45900</v>
       </c>
       <c r="B237" t="n">
-        <v>74.51316070556641</v>
+        <v>74.51315307617188</v>
       </c>
       <c r="C237" t="n">
         <v>77.37000274658203</v>
@@ -6840,7 +6852,7 @@
       </c>
     </row>
     <row r="238">
-      <c r="A238" s="1" t="n">
+      <c r="A238" s="2" t="n">
         <v>45930</v>
       </c>
       <c r="B238" t="n">
@@ -6869,11 +6881,11 @@
       </c>
     </row>
     <row r="239">
-      <c r="A239" s="1" t="n">
+      <c r="A239" s="2" t="n">
         <v>45961</v>
       </c>
       <c r="B239" t="n">
-        <v>62.52831649780273</v>
+        <v>62.5283203125</v>
       </c>
       <c r="C239" t="n">
         <v>64.58999633789062</v>
@@ -6898,7 +6910,7 @@
       </c>
     </row>
     <row r="240">
-      <c r="A240" s="1" t="n">
+      <c r="A240" s="2" t="n">
         <v>45991</v>
       </c>
       <c r="B240" t="n">
@@ -6927,7 +6939,7 @@
       </c>
     </row>
     <row r="241">
-      <c r="A241" s="1" t="n">
+      <c r="A241" s="2" t="n">
         <v>46022</v>
       </c>
       <c r="B241" t="n">
@@ -6956,7 +6968,7 @@
       </c>
     </row>
     <row r="242">
-      <c r="A242" s="1" t="n">
+      <c r="A242" s="2" t="n">
         <v>46053</v>
       </c>
       <c r="B242" t="n">
@@ -6985,7 +6997,7 @@
       </c>
     </row>
     <row r="243">
-      <c r="A243" s="1" t="n">
+      <c r="A243" s="2" t="n">
         <v>46081</v>
       </c>
       <c r="B243" t="n">
@@ -7014,7 +7026,7 @@
       </c>
     </row>
     <row r="244">
-      <c r="A244" s="1" t="n">
+      <c r="A244" s="2" t="n">
         <v>46112</v>
       </c>
       <c r="B244" t="n">
@@ -7043,11 +7055,11 @@
       </c>
     </row>
     <row r="245">
-      <c r="A245" s="1" t="n">
+      <c r="A245" s="2" t="n">
         <v>46142</v>
       </c>
       <c r="B245" t="n">
-        <v>43.50508499145508</v>
+        <v>43.50508117675781</v>
       </c>
       <c r="C245" t="n">
         <v>44.36000061035156</v>
@@ -7072,7 +7084,7 @@
       </c>
     </row>
     <row r="246">
-      <c r="A246" s="1" t="n">
+      <c r="A246" s="2" t="n">
         <v>46173</v>
       </c>
       <c r="B246" t="n">
@@ -7101,7 +7113,7 @@
       </c>
     </row>
     <row r="247">
-      <c r="A247" s="1" t="n">
+      <c r="A247" s="2" t="n">
         <v>46203</v>
       </c>
       <c r="B247" t="n">
@@ -7130,7 +7142,7 @@
       </c>
     </row>
     <row r="248">
-      <c r="A248" s="1" t="n">
+      <c r="A248" s="2" t="n">
         <v>46234</v>
       </c>
       <c r="B248" t="n">
@@ -7159,7 +7171,7 @@
       </c>
     </row>
     <row r="249">
-      <c r="A249" s="1" t="n">
+      <c r="A249" s="2" t="n">
         <v>46265</v>
       </c>
       <c r="B249" t="n">
@@ -7188,32 +7200,32 @@
       </c>
     </row>
     <row r="250">
-      <c r="A250" s="1" t="n">
+      <c r="A250" s="2" t="n">
         <v>46295</v>
       </c>
       <c r="B250" t="n">
-        <v>36.04999923706055</v>
+        <v>35.9900016784668</v>
       </c>
       <c r="C250" t="n">
-        <v>36.04999923706055</v>
+        <v>35.9900016784668</v>
       </c>
       <c r="D250" t="n">
-        <v>518487700</v>
+        <v>557697900</v>
       </c>
       <c r="E250" t="n">
         <v>2.1</v>
       </c>
       <c r="F250" t="n">
-        <v>17.16666630336216</v>
+        <v>17.13809603736514</v>
       </c>
       <c r="G250" t="n">
         <v>1479800000</v>
       </c>
       <c r="H250" t="n">
-        <v>53346788871.0022</v>
+        <v>53258004483.79517</v>
       </c>
       <c r="I250" t="n">
-        <v>0.3503768752534126</v>
+        <v>0.3768738343019327</v>
       </c>
     </row>
   </sheetData>
@@ -7245,75 +7257,75 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>start</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>eps_trimestral</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>origen</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>filed_ttm</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>39600</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>39691</v>
       </c>
-      <c r="C2" s="1" t="n">
+      <c r="C2" s="2" t="n">
         <v>40094</v>
       </c>
       <c r="D2" t="inlineStr">
@@ -7349,13 +7361,13 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>39692</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>39782</v>
       </c>
-      <c r="C3" s="1" t="n">
+      <c r="C3" s="2" t="n">
         <v>40184</v>
       </c>
       <c r="D3" t="inlineStr">
@@ -7391,13 +7403,13 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>39783</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>39872</v>
       </c>
-      <c r="C4" s="1" t="n">
+      <c r="C4" s="2" t="n">
         <v>40275</v>
       </c>
       <c r="D4" t="inlineStr">
@@ -7433,13 +7445,13 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>39873</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>39964</v>
       </c>
-      <c r="C5" s="1" t="n">
+      <c r="C5" s="2" t="n">
         <v>40379</v>
       </c>
       <c r="D5" t="inlineStr">
@@ -7466,7 +7478,7 @@
       <c r="I5" t="n">
         <v>0.7575</v>
       </c>
-      <c r="J5" s="1" t="n">
+      <c r="J5" s="2" t="n">
         <v>40379</v>
       </c>
       <c r="K5" t="n">
@@ -7479,13 +7491,13 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>39965</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>40056</v>
       </c>
-      <c r="C6" s="1" t="n">
+      <c r="C6" s="2" t="n">
         <v>40094</v>
       </c>
       <c r="D6" t="inlineStr">
@@ -7512,7 +7524,7 @@
       <c r="I6" t="n">
         <v>0.76</v>
       </c>
-      <c r="J6" s="1" t="n">
+      <c r="J6" s="2" t="n">
         <v>40379</v>
       </c>
       <c r="K6" t="n">
@@ -7525,13 +7537,13 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>40057</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>40147</v>
       </c>
-      <c r="C7" s="1" t="n">
+      <c r="C7" s="2" t="n">
         <v>40184</v>
       </c>
       <c r="D7" t="inlineStr">
@@ -7558,7 +7570,7 @@
       <c r="I7" t="n">
         <v>0.75</v>
       </c>
-      <c r="J7" s="1" t="n">
+      <c r="J7" s="2" t="n">
         <v>40379</v>
       </c>
       <c r="K7" t="n">
@@ -7571,13 +7583,13 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>40148</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>40237</v>
       </c>
-      <c r="C8" s="1" t="n">
+      <c r="C8" s="2" t="n">
         <v>40275</v>
       </c>
       <c r="D8" t="inlineStr">
@@ -7604,7 +7616,7 @@
       <c r="I8" t="n">
         <v>0.8774999999999999</v>
       </c>
-      <c r="J8" s="1" t="n">
+      <c r="J8" s="2" t="n">
         <v>40379</v>
       </c>
       <c r="K8" t="n">
@@ -7617,13 +7629,13 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>40238</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>40329</v>
       </c>
-      <c r="C9" s="1" t="n">
+      <c r="C9" s="2" t="n">
         <v>40379</v>
       </c>
       <c r="D9" t="inlineStr">
@@ -7650,7 +7662,7 @@
       <c r="I9" t="n">
         <v>0.9649999999999999</v>
       </c>
-      <c r="J9" s="1" t="n">
+      <c r="J9" s="2" t="n">
         <v>40379</v>
       </c>
       <c r="K9" t="n">
@@ -7663,13 +7675,13 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>40330</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>40421</v>
       </c>
-      <c r="C10" s="1" t="n">
+      <c r="C10" s="2" t="n">
         <v>40457</v>
       </c>
       <c r="D10" t="inlineStr">
@@ -7696,7 +7708,7 @@
       <c r="I10" t="n">
         <v>0.9899999999999999</v>
       </c>
-      <c r="J10" s="1" t="n">
+      <c r="J10" s="2" t="n">
         <v>40457</v>
       </c>
       <c r="K10" t="n">
@@ -7709,13 +7721,13 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>40422</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>40512</v>
       </c>
-      <c r="C11" s="1" t="n">
+      <c r="C11" s="2" t="n">
         <v>40549</v>
       </c>
       <c r="D11" t="inlineStr">
@@ -7742,7 +7754,7 @@
       <c r="I11" t="n">
         <v>1.035</v>
       </c>
-      <c r="J11" s="1" t="n">
+      <c r="J11" s="2" t="n">
         <v>40549</v>
       </c>
       <c r="K11" t="n">
@@ -7755,13 +7767,13 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>40513</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>40602</v>
       </c>
-      <c r="C12" s="1" t="n">
+      <c r="C12" s="2" t="n">
         <v>40639</v>
       </c>
       <c r="D12" t="inlineStr">
@@ -7788,7 +7800,7 @@
       <c r="I12" t="n">
         <v>1.0525</v>
       </c>
-      <c r="J12" s="1" t="n">
+      <c r="J12" s="2" t="n">
         <v>40639</v>
       </c>
       <c r="K12" t="n">
@@ -7801,13 +7813,13 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>40603</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>40694</v>
       </c>
-      <c r="C13" s="1" t="n">
+      <c r="C13" s="2" t="n">
         <v>40746</v>
       </c>
       <c r="D13" t="inlineStr">
@@ -7834,7 +7846,7 @@
       <c r="I13" t="n">
         <v>1.0975</v>
       </c>
-      <c r="J13" s="1" t="n">
+      <c r="J13" s="2" t="n">
         <v>40746</v>
       </c>
       <c r="K13" t="n">
@@ -7847,13 +7859,13 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>40695</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>40786</v>
       </c>
-      <c r="C14" s="1" t="n">
+      <c r="C14" s="2" t="n">
         <v>40822</v>
       </c>
       <c r="D14" t="inlineStr">
@@ -7880,7 +7892,7 @@
       <c r="I14" t="n">
         <v>1.1525</v>
       </c>
-      <c r="J14" s="1" t="n">
+      <c r="J14" s="2" t="n">
         <v>40822</v>
       </c>
       <c r="K14" t="n">
@@ -7893,13 +7905,13 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>40787</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>40877</v>
       </c>
-      <c r="C15" s="1" t="n">
+      <c r="C15" s="2" t="n">
         <v>40913</v>
       </c>
       <c r="D15" t="inlineStr">
@@ -7926,7 +7938,7 @@
       <c r="I15" t="n">
         <v>1.1675</v>
       </c>
-      <c r="J15" s="1" t="n">
+      <c r="J15" s="2" t="n">
         <v>40913</v>
       </c>
       <c r="K15" t="n">
@@ -7939,13 +7951,13 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>40878</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>40968</v>
       </c>
-      <c r="C16" s="1" t="n">
+      <c r="C16" s="2" t="n">
         <v>41005</v>
       </c>
       <c r="D16" t="inlineStr">
@@ -7972,7 +7984,7 @@
       <c r="I16" t="n">
         <v>1.1975</v>
       </c>
-      <c r="J16" s="1" t="n">
+      <c r="J16" s="2" t="n">
         <v>41005</v>
       </c>
       <c r="K16" t="n">
@@ -7985,13 +7997,13 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>40969</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>41060</v>
       </c>
-      <c r="C17" s="1" t="n">
+      <c r="C17" s="2" t="n">
         <v>41114</v>
       </c>
       <c r="D17" t="inlineStr">
@@ -8018,7 +8030,7 @@
       <c r="I17" t="n">
         <v>1.1825</v>
       </c>
-      <c r="J17" s="1" t="n">
+      <c r="J17" s="2" t="n">
         <v>41114</v>
       </c>
       <c r="K17" t="n">
@@ -8031,13 +8043,13 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>41061</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>41152</v>
       </c>
-      <c r="C18" s="1" t="n">
+      <c r="C18" s="2" t="n">
         <v>41191</v>
       </c>
       <c r="D18" t="inlineStr">
@@ -8064,7 +8076,7 @@
       <c r="I18" t="n">
         <v>1.15</v>
       </c>
-      <c r="J18" s="1" t="n">
+      <c r="J18" s="2" t="n">
         <v>41191</v>
       </c>
       <c r="K18" t="n">
@@ -8077,13 +8089,13 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>41153</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>41243</v>
       </c>
-      <c r="C19" s="1" t="n">
+      <c r="C19" s="2" t="n">
         <v>41283</v>
       </c>
       <c r="D19" t="inlineStr">
@@ -8110,7 +8122,7 @@
       <c r="I19" t="n">
         <v>1.11</v>
       </c>
-      <c r="J19" s="1" t="n">
+      <c r="J19" s="2" t="n">
         <v>41283</v>
       </c>
       <c r="K19" t="n">
@@ -8123,13 +8135,13 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>41244</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>41333</v>
       </c>
-      <c r="C20" s="1" t="n">
+      <c r="C20" s="2" t="n">
         <v>41368</v>
       </c>
       <c r="D20" t="inlineStr">
@@ -8156,7 +8168,7 @@
       <c r="I20" t="n">
         <v>1.285</v>
       </c>
-      <c r="J20" s="1" t="n">
+      <c r="J20" s="2" t="n">
         <v>41368</v>
       </c>
       <c r="K20" t="n">
@@ -8169,13 +8181,13 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>41334</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>41425</v>
       </c>
-      <c r="C21" s="1" t="n">
+      <c r="C21" s="2" t="n">
         <v>41478</v>
       </c>
       <c r="D21" t="inlineStr">
@@ -8202,7 +8214,7 @@
       <c r="I21" t="n">
         <v>1.355</v>
       </c>
-      <c r="J21" s="1" t="n">
+      <c r="J21" s="2" t="n">
         <v>41478</v>
       </c>
       <c r="K21" t="n">
@@ -8215,13 +8227,13 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>41426</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>41517</v>
       </c>
-      <c r="C22" s="1" t="n">
+      <c r="C22" s="2" t="n">
         <v>41554</v>
       </c>
       <c r="D22" t="inlineStr">
@@ -8248,7 +8260,7 @@
       <c r="I22" t="n">
         <v>1.4775</v>
       </c>
-      <c r="J22" s="1" t="n">
+      <c r="J22" s="2" t="n">
         <v>41554</v>
       </c>
       <c r="K22" t="n">
@@ -8261,13 +8273,13 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>41518</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>41608</v>
       </c>
-      <c r="C23" s="1" t="n">
+      <c r="C23" s="2" t="n">
         <v>41646</v>
       </c>
       <c r="D23" t="inlineStr">
@@ -8294,7 +8306,7 @@
       <c r="I23" t="n">
         <v>1.5625</v>
       </c>
-      <c r="J23" s="1" t="n">
+      <c r="J23" s="2" t="n">
         <v>41646</v>
       </c>
       <c r="K23" t="n">
@@ -8307,13 +8319,13 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>41609</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>41698</v>
       </c>
-      <c r="C24" s="1" t="n">
+      <c r="C24" s="2" t="n">
         <v>41736</v>
       </c>
       <c r="D24" t="inlineStr">
@@ -8340,7 +8352,7 @@
       <c r="I24" t="n">
         <v>1.4675</v>
       </c>
-      <c r="J24" s="1" t="n">
+      <c r="J24" s="2" t="n">
         <v>41736</v>
       </c>
       <c r="K24" t="n">
@@ -8353,13 +8365,13 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>41699</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>41790</v>
       </c>
-      <c r="C25" s="1" t="n">
+      <c r="C25" s="2" t="n">
         <v>41845</v>
       </c>
       <c r="D25" t="inlineStr">
@@ -8386,7 +8398,7 @@
       <c r="I25" t="n">
         <v>1.485</v>
       </c>
-      <c r="J25" s="1" t="n">
+      <c r="J25" s="2" t="n">
         <v>41845</v>
       </c>
       <c r="K25" t="n">
@@ -8399,13 +8411,13 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>41791</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>41882</v>
       </c>
-      <c r="C26" s="1" t="n">
+      <c r="C26" s="2" t="n">
         <v>41919</v>
       </c>
       <c r="D26" t="inlineStr">
@@ -8432,7 +8444,7 @@
       <c r="I26" t="n">
         <v>1.6</v>
       </c>
-      <c r="J26" s="1" t="n">
+      <c r="J26" s="2" t="n">
         <v>41919</v>
       </c>
       <c r="K26" t="n">
@@ -8445,13 +8457,13 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>41883</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>41973</v>
       </c>
-      <c r="C27" s="1" t="n">
+      <c r="C27" s="2" t="n">
         <v>42011</v>
       </c>
       <c r="D27" t="inlineStr">
@@ -8478,7 +8490,7 @@
       <c r="I27" t="n">
         <v>1.675</v>
       </c>
-      <c r="J27" s="1" t="n">
+      <c r="J27" s="2" t="n">
         <v>42011</v>
       </c>
       <c r="K27" t="n">
@@ -8491,13 +8503,13 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>41974</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>42063</v>
       </c>
-      <c r="C28" s="1" t="n">
+      <c r="C28" s="2" t="n">
         <v>42101</v>
       </c>
       <c r="D28" t="inlineStr">
@@ -8524,7 +8536,7 @@
       <c r="I28" t="n">
         <v>1.74</v>
       </c>
-      <c r="J28" s="1" t="n">
+      <c r="J28" s="2" t="n">
         <v>42101</v>
       </c>
       <c r="K28" t="n">
@@ -8537,13 +8549,13 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>42064</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>42155</v>
       </c>
-      <c r="C29" s="1" t="n">
+      <c r="C29" s="2" t="n">
         <v>42208</v>
       </c>
       <c r="D29" t="inlineStr">
@@ -8570,7 +8582,7 @@
       <c r="I29" t="n">
         <v>1.85</v>
       </c>
-      <c r="J29" s="1" t="n">
+      <c r="J29" s="2" t="n">
         <v>42208</v>
       </c>
       <c r="K29" t="n">
@@ -8583,13 +8595,13 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>42156</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>42247</v>
       </c>
-      <c r="C30" s="1" t="n">
+      <c r="C30" s="2" t="n">
         <v>42283</v>
       </c>
       <c r="D30" t="inlineStr">
@@ -8616,7 +8628,7 @@
       <c r="I30" t="n">
         <v>1.975</v>
       </c>
-      <c r="J30" s="1" t="n">
+      <c r="J30" s="2" t="n">
         <v>42283</v>
       </c>
       <c r="K30" t="n">
@@ -8629,13 +8641,13 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>42248</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>42338</v>
       </c>
-      <c r="C31" s="1" t="n">
+      <c r="C31" s="2" t="n">
         <v>42375</v>
       </c>
       <c r="D31" t="inlineStr">
@@ -8662,7 +8674,7 @@
       <c r="I31" t="n">
         <v>2.055</v>
       </c>
-      <c r="J31" s="1" t="n">
+      <c r="J31" s="2" t="n">
         <v>42375</v>
       </c>
       <c r="K31" t="n">
@@ -8675,13 +8687,13 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>42339</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>42429</v>
       </c>
-      <c r="C32" s="1" t="n">
+      <c r="C32" s="2" t="n">
         <v>42465</v>
       </c>
       <c r="D32" t="inlineStr">
@@ -8708,7 +8720,7 @@
       <c r="I32" t="n">
         <v>2.16</v>
       </c>
-      <c r="J32" s="1" t="n">
+      <c r="J32" s="2" t="n">
         <v>42465</v>
       </c>
       <c r="K32" t="n">
@@ -8721,13 +8733,13 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>42430</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>42521</v>
       </c>
-      <c r="C33" s="1" t="n">
+      <c r="C33" s="2" t="n">
         <v>42572</v>
       </c>
       <c r="D33" t="inlineStr">
@@ -8754,7 +8766,7 @@
       <c r="I33" t="n">
         <v>2.16</v>
       </c>
-      <c r="J33" s="1" t="n">
+      <c r="J33" s="2" t="n">
         <v>42572</v>
       </c>
       <c r="K33" t="n">
@@ -8767,13 +8779,13 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>42522</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>42613</v>
       </c>
-      <c r="C34" s="1" t="n">
+      <c r="C34" s="2" t="n">
         <v>42654</v>
       </c>
       <c r="D34" t="inlineStr">
@@ -8800,7 +8812,7 @@
       <c r="I34" t="n">
         <v>2.22</v>
       </c>
-      <c r="J34" s="1" t="n">
+      <c r="J34" s="2" t="n">
         <v>42654</v>
       </c>
       <c r="K34" t="n">
@@ -8813,13 +8825,13 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>42614</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>42704</v>
       </c>
-      <c r="C35" s="1" t="n">
+      <c r="C35" s="2" t="n">
         <v>42740</v>
       </c>
       <c r="D35" t="inlineStr">
@@ -8846,7 +8858,7 @@
       <c r="I35" t="n">
         <v>2.27</v>
       </c>
-      <c r="J35" s="1" t="n">
+      <c r="J35" s="2" t="n">
         <v>42740</v>
       </c>
       <c r="K35" t="n">
@@ -8859,13 +8871,13 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>42705</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>42794</v>
       </c>
-      <c r="C36" s="1" t="n">
+      <c r="C36" s="2" t="n">
         <v>42829</v>
       </c>
       <c r="D36" t="inlineStr">
@@ -8892,7 +8904,7 @@
       <c r="I36" t="n">
         <v>2.4</v>
       </c>
-      <c r="J36" s="1" t="n">
+      <c r="J36" s="2" t="n">
         <v>42829</v>
       </c>
       <c r="K36" t="n">
@@ -8905,13 +8917,13 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>42795</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>42886</v>
       </c>
-      <c r="C37" s="1" t="n">
+      <c r="C37" s="2" t="n">
         <v>42936</v>
       </c>
       <c r="D37" t="inlineStr">
@@ -8938,7 +8950,7 @@
       <c r="I37" t="n">
         <v>2.51</v>
       </c>
-      <c r="J37" s="1" t="n">
+      <c r="J37" s="2" t="n">
         <v>42936</v>
       </c>
       <c r="K37" t="n">
@@ -8951,13 +8963,13 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>42887</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>42978</v>
       </c>
-      <c r="C38" s="1" t="n">
+      <c r="C38" s="2" t="n">
         <v>43014</v>
       </c>
       <c r="D38" t="inlineStr">
@@ -8984,7 +8996,7 @@
       <c r="I38" t="n">
         <v>2.35</v>
       </c>
-      <c r="J38" s="1" t="n">
+      <c r="J38" s="2" t="n">
         <v>43014</v>
       </c>
       <c r="K38" t="n">
@@ -8997,13 +9009,13 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>42979</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>43069</v>
       </c>
-      <c r="C39" s="1" t="n">
+      <c r="C39" s="2" t="n">
         <v>43105</v>
       </c>
       <c r="D39" t="inlineStr">
@@ -9030,7 +9042,7 @@
       <c r="I39" t="n">
         <v>2.31</v>
       </c>
-      <c r="J39" s="1" t="n">
+      <c r="J39" s="2" t="n">
         <v>43105</v>
       </c>
       <c r="K39" t="n">
@@ -9043,13 +9055,13 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>43070</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>43159</v>
       </c>
-      <c r="C40" s="1" t="n">
+      <c r="C40" s="2" t="n">
         <v>43195</v>
       </c>
       <c r="D40" t="inlineStr">
@@ -9076,7 +9088,7 @@
       <c r="I40" t="n">
         <v>1.06</v>
       </c>
-      <c r="J40" s="1" t="n">
+      <c r="J40" s="2" t="n">
         <v>43195</v>
       </c>
       <c r="K40" t="n">
@@ -9089,13 +9101,13 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>43160</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>43251</v>
       </c>
-      <c r="C41" s="1" t="n">
+      <c r="C41" s="2" t="n">
         <v>43306</v>
       </c>
       <c r="D41" t="inlineStr">
@@ -9122,7 +9134,7 @@
       <c r="I41" t="n">
         <v>1.17</v>
       </c>
-      <c r="J41" s="1" t="n">
+      <c r="J41" s="2" t="n">
         <v>43306</v>
       </c>
       <c r="K41" t="n">
@@ -9135,13 +9147,13 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>43252</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>43343</v>
       </c>
-      <c r="C42" s="1" t="n">
+      <c r="C42" s="2" t="n">
         <v>43378</v>
       </c>
       <c r="D42" t="inlineStr">
@@ -9168,7 +9180,7 @@
       <c r="I42" t="n">
         <v>1.27</v>
       </c>
-      <c r="J42" s="1" t="n">
+      <c r="J42" s="2" t="n">
         <v>43378</v>
       </c>
       <c r="K42" t="n">
@@ -9181,13 +9193,13 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>43344</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>43434</v>
       </c>
-      <c r="C43" s="1" t="n">
+      <c r="C43" s="2" t="n">
         <v>43473</v>
       </c>
       <c r="D43" t="inlineStr">
@@ -9214,7 +9226,7 @@
       <c r="I43" t="n">
         <v>1.33</v>
       </c>
-      <c r="J43" s="1" t="n">
+      <c r="J43" s="2" t="n">
         <v>43473</v>
       </c>
       <c r="K43" t="n">
@@ -9227,13 +9239,13 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>43435</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>43524</v>
       </c>
-      <c r="C44" s="1" t="n">
+      <c r="C44" s="2" t="n">
         <v>43559</v>
       </c>
       <c r="D44" t="inlineStr">
@@ -9260,7 +9272,7 @@
       <c r="I44" t="n">
         <v>2.58</v>
       </c>
-      <c r="J44" s="1" t="n">
+      <c r="J44" s="2" t="n">
         <v>43559</v>
       </c>
       <c r="K44" t="n">
@@ -9273,13 +9285,13 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>43525</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>43616</v>
       </c>
-      <c r="C45" s="1" t="n">
+      <c r="C45" s="2" t="n">
         <v>43669</v>
       </c>
       <c r="D45" t="inlineStr">
@@ -9306,7 +9318,7 @@
       <c r="I45" t="n">
         <v>2.49</v>
       </c>
-      <c r="J45" s="1" t="n">
+      <c r="J45" s="2" t="n">
         <v>43669</v>
       </c>
       <c r="K45" t="n">
@@ -9319,13 +9331,13 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>43617</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>43708</v>
       </c>
-      <c r="C46" s="1" t="n">
+      <c r="C46" s="2" t="n">
         <v>43742</v>
       </c>
       <c r="D46" t="inlineStr">
@@ -9352,7 +9364,7 @@
       <c r="I46" t="n">
         <v>2.68</v>
       </c>
-      <c r="J46" s="1" t="n">
+      <c r="J46" s="2" t="n">
         <v>43742</v>
       </c>
       <c r="K46" t="n">
@@ -9365,13 +9377,13 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>43709</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>43799</v>
       </c>
-      <c r="C47" s="1" t="n">
+      <c r="C47" s="2" t="n">
         <v>43837</v>
       </c>
       <c r="D47" t="inlineStr">
@@ -9398,7 +9410,7 @@
       <c r="I47" t="n">
         <v>2.86</v>
       </c>
-      <c r="J47" s="1" t="n">
+      <c r="J47" s="2" t="n">
         <v>43837</v>
       </c>
       <c r="K47" t="n">
@@ -9411,13 +9423,13 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>43800</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>43890</v>
       </c>
-      <c r="C48" s="1" t="n">
+      <c r="C48" s="2" t="n">
         <v>43928</v>
       </c>
       <c r="D48" t="inlineStr">
@@ -9444,7 +9456,7 @@
       <c r="I48" t="n">
         <v>2.71</v>
       </c>
-      <c r="J48" s="1" t="n">
+      <c r="J48" s="2" t="n">
         <v>43928</v>
       </c>
       <c r="K48" t="n">
@@ -9457,13 +9469,13 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>43891</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>43982</v>
       </c>
-      <c r="C49" s="1" t="n">
+      <c r="C49" s="2" t="n">
         <v>44036</v>
       </c>
       <c r="D49" t="inlineStr">
@@ -9490,7 +9502,7 @@
       <c r="I49" t="n">
         <v>1.6</v>
       </c>
-      <c r="J49" s="1" t="n">
+      <c r="J49" s="2" t="n">
         <v>44036</v>
       </c>
       <c r="K49" t="n">
@@ -9503,13 +9515,13 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>43983</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>44074</v>
       </c>
-      <c r="C50" s="1" t="n">
+      <c r="C50" s="2" t="n">
         <v>44112</v>
       </c>
       <c r="D50" t="inlineStr">
@@ -9536,7 +9548,7 @@
       <c r="I50" t="n">
         <v>1.69</v>
       </c>
-      <c r="J50" s="1" t="n">
+      <c r="J50" s="2" t="n">
         <v>44112</v>
       </c>
       <c r="K50" t="n">
@@ -9549,13 +9561,13 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>44075</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>44165</v>
       </c>
-      <c r="C51" s="1" t="n">
+      <c r="C51" s="2" t="n">
         <v>44201</v>
       </c>
       <c r="D51" t="inlineStr">
@@ -9582,7 +9594,7 @@
       <c r="I51" t="n">
         <v>1.77</v>
       </c>
-      <c r="J51" s="1" t="n">
+      <c r="J51" s="2" t="n">
         <v>44201</v>
       </c>
       <c r="K51" t="n">
@@ -9595,13 +9607,13 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>44166</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>44255</v>
       </c>
-      <c r="C52" s="1" t="n">
+      <c r="C52" s="2" t="n">
         <v>44288</v>
       </c>
       <c r="D52" t="inlineStr">
@@ -9628,7 +9640,7 @@
       <c r="I52" t="n">
         <v>2.14</v>
       </c>
-      <c r="J52" s="1" t="n">
+      <c r="J52" s="2" t="n">
         <v>44288</v>
       </c>
       <c r="K52" t="n">
@@ -9641,13 +9653,13 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>44256</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>44347</v>
       </c>
-      <c r="C53" s="1" t="n">
+      <c r="C53" s="2" t="n">
         <v>44397</v>
       </c>
       <c r="D53" t="inlineStr">
@@ -9674,7 +9686,7 @@
       <c r="I53" t="n">
         <v>3.56</v>
       </c>
-      <c r="J53" s="1" t="n">
+      <c r="J53" s="2" t="n">
         <v>44397</v>
       </c>
       <c r="K53" t="n">
@@ -9687,13 +9699,13 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>44348</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>44439</v>
       </c>
-      <c r="C54" s="1" t="n">
+      <c r="C54" s="2" t="n">
         <v>44474</v>
       </c>
       <c r="D54" t="inlineStr">
@@ -9720,7 +9732,7 @@
       <c r="I54" t="n">
         <v>3.77</v>
       </c>
-      <c r="J54" s="1" t="n">
+      <c r="J54" s="2" t="n">
         <v>44474</v>
       </c>
       <c r="K54" t="n">
@@ -9733,13 +9745,13 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>44440</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>44530</v>
       </c>
-      <c r="C55" s="1" t="n">
+      <c r="C55" s="2" t="n">
         <v>44567</v>
       </c>
       <c r="D55" t="inlineStr">
@@ -9766,7 +9778,7 @@
       <c r="I55" t="n">
         <v>3.82</v>
       </c>
-      <c r="J55" s="1" t="n">
+      <c r="J55" s="2" t="n">
         <v>44567</v>
       </c>
       <c r="K55" t="n">
@@ -9779,13 +9791,13 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>44531</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>44620</v>
       </c>
-      <c r="C56" s="1" t="n">
+      <c r="C56" s="2" t="n">
         <v>44656</v>
       </c>
       <c r="D56" t="inlineStr">
@@ -9812,7 +9824,7 @@
       <c r="I56" t="n">
         <v>3.79</v>
       </c>
-      <c r="J56" s="1" t="n">
+      <c r="J56" s="2" t="n">
         <v>44656</v>
       </c>
       <c r="K56" t="n">
@@ -9825,13 +9837,13 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>44621</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="2" t="n">
         <v>44712</v>
       </c>
-      <c r="C57" s="1" t="n">
+      <c r="C57" s="2" t="n">
         <v>44763</v>
       </c>
       <c r="D57" t="inlineStr">
@@ -9858,7 +9870,7 @@
       <c r="I57" t="n">
         <v>3.75</v>
       </c>
-      <c r="J57" s="1" t="n">
+      <c r="J57" s="2" t="n">
         <v>44763</v>
       </c>
       <c r="K57" t="n">
@@ -9871,13 +9883,13 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>44713</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="2" t="n">
         <v>44804</v>
       </c>
-      <c r="C58" s="1" t="n">
+      <c r="C58" s="2" t="n">
         <v>44840</v>
       </c>
       <c r="D58" t="inlineStr">
@@ -9904,7 +9916,7 @@
       <c r="I58" t="n">
         <v>3.52</v>
       </c>
-      <c r="J58" s="1" t="n">
+      <c r="J58" s="2" t="n">
         <v>44840</v>
       </c>
       <c r="K58" t="n">
@@ -9917,13 +9929,13 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>44805</v>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="2" t="n">
         <v>44895</v>
       </c>
-      <c r="C59" s="1" t="n">
+      <c r="C59" s="2" t="n">
         <v>44931</v>
       </c>
       <c r="D59" t="inlineStr">
@@ -9950,7 +9962,7 @@
       <c r="I59" t="n">
         <v>3.54</v>
       </c>
-      <c r="J59" s="1" t="n">
+      <c r="J59" s="2" t="n">
         <v>44931</v>
       </c>
       <c r="K59" t="n">
@@ -9963,13 +9975,13 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>44896</v>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="2" t="n">
         <v>44985</v>
       </c>
-      <c r="C60" s="1" t="n">
+      <c r="C60" s="2" t="n">
         <v>45022</v>
       </c>
       <c r="D60" t="inlineStr">
@@ -9996,7 +10008,7 @@
       <c r="I60" t="n">
         <v>3.46</v>
       </c>
-      <c r="J60" s="1" t="n">
+      <c r="J60" s="2" t="n">
         <v>45022</v>
       </c>
       <c r="K60" t="n">
@@ -10009,13 +10021,13 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>44986</v>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="2" t="n">
         <v>45077</v>
       </c>
-      <c r="C61" s="1" t="n">
+      <c r="C61" s="2" t="n">
         <v>45127</v>
       </c>
       <c r="D61" t="inlineStr">
@@ -10042,7 +10054,7 @@
       <c r="I61" t="n">
         <v>3.23</v>
       </c>
-      <c r="J61" s="1" t="n">
+      <c r="J61" s="2" t="n">
         <v>45127</v>
       </c>
       <c r="K61" t="n">
@@ -10055,13 +10067,13 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>45078</v>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="2" t="n">
         <v>45169</v>
       </c>
-      <c r="C62" s="1" t="n">
+      <c r="C62" s="2" t="n">
         <v>45205</v>
       </c>
       <c r="D62" t="inlineStr">
@@ -10088,7 +10100,7 @@
       <c r="I62" t="n">
         <v>3.24</v>
       </c>
-      <c r="J62" s="1" t="n">
+      <c r="J62" s="2" t="n">
         <v>45205</v>
       </c>
       <c r="K62" t="n">
@@ -10101,13 +10113,13 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>45170</v>
       </c>
-      <c r="B63" s="1" t="n">
+      <c r="B63" s="2" t="n">
         <v>45260</v>
       </c>
-      <c r="C63" s="1" t="n">
+      <c r="C63" s="2" t="n">
         <v>45296</v>
       </c>
       <c r="D63" t="inlineStr">
@@ -10134,7 +10146,7 @@
       <c r="I63" t="n">
         <v>3.42</v>
       </c>
-      <c r="J63" s="1" t="n">
+      <c r="J63" s="2" t="n">
         <v>45296</v>
       </c>
       <c r="K63" t="n">
@@ -10147,13 +10159,13 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>45261</v>
       </c>
-      <c r="B64" s="1" t="n">
+      <c r="B64" s="2" t="n">
         <v>45351</v>
       </c>
-      <c r="C64" s="1" t="n">
+      <c r="C64" s="2" t="n">
         <v>45386</v>
       </c>
       <c r="D64" t="inlineStr">
@@ -10180,7 +10192,7 @@
       <c r="I64" t="n">
         <v>3.399999999999999</v>
       </c>
-      <c r="J64" s="1" t="n">
+      <c r="J64" s="2" t="n">
         <v>45386</v>
       </c>
       <c r="K64" t="n">
@@ -10193,13 +10205,13 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>45352</v>
       </c>
-      <c r="B65" s="1" t="n">
+      <c r="B65" s="2" t="n">
         <v>45443</v>
       </c>
-      <c r="C65" s="1" t="n">
+      <c r="C65" s="2" t="n">
         <v>45498</v>
       </c>
       <c r="D65" t="inlineStr">
@@ -10226,7 +10238,7 @@
       <c r="I65" t="n">
         <v>3.73</v>
       </c>
-      <c r="J65" s="1" t="n">
+      <c r="J65" s="2" t="n">
         <v>45498</v>
       </c>
       <c r="K65" t="n">
@@ -10239,13 +10251,13 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>45444</v>
       </c>
-      <c r="B66" s="1" t="n">
+      <c r="B66" s="2" t="n">
         <v>45535</v>
       </c>
-      <c r="C66" s="1" t="n">
+      <c r="C66" s="2" t="n">
         <v>45572</v>
       </c>
       <c r="D66" t="inlineStr">
@@ -10272,7 +10284,7 @@
       <c r="I66" t="n">
         <v>3.49</v>
       </c>
-      <c r="J66" s="1" t="n">
+      <c r="J66" s="2" t="n">
         <v>45572</v>
       </c>
       <c r="K66" t="n">
@@ -10285,13 +10297,13 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>45536</v>
       </c>
-      <c r="B67" s="1" t="n">
+      <c r="B67" s="2" t="n">
         <v>45626</v>
       </c>
-      <c r="C67" s="1" t="n">
+      <c r="C67" s="2" t="n">
         <v>45660</v>
       </c>
       <c r="D67" t="inlineStr">
@@ -10318,7 +10330,7 @@
       <c r="I67" t="n">
         <v>3.24</v>
       </c>
-      <c r="J67" s="1" t="n">
+      <c r="J67" s="2" t="n">
         <v>45660</v>
       </c>
       <c r="K67" t="n">
@@ -10331,13 +10343,13 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>45627</v>
       </c>
-      <c r="B68" s="1" t="n">
+      <c r="B68" s="2" t="n">
         <v>45716</v>
       </c>
-      <c r="C68" s="1" t="n">
+      <c r="C68" s="2" t="n">
         <v>45750</v>
       </c>
       <c r="D68" t="inlineStr">
@@ -10364,7 +10376,7 @@
       <c r="I68" t="n">
         <v>3.01</v>
       </c>
-      <c r="J68" s="1" t="n">
+      <c r="J68" s="2" t="n">
         <v>45750</v>
       </c>
       <c r="K68" t="n">
@@ -10377,13 +10389,13 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>45717</v>
       </c>
-      <c r="B69" s="1" t="n">
+      <c r="B69" s="2" t="n">
         <v>45808</v>
       </c>
-      <c r="C69" s="1" t="n">
+      <c r="C69" s="2" t="n">
         <v>45855</v>
       </c>
       <c r="D69" t="inlineStr">
@@ -10410,7 +10422,7 @@
       <c r="I69" t="n">
         <v>2.16</v>
       </c>
-      <c r="J69" s="1" t="n">
+      <c r="J69" s="2" t="n">
         <v>45855</v>
       </c>
       <c r="K69" t="n">
@@ -10423,13 +10435,13 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>45809</v>
       </c>
-      <c r="B70" s="1" t="n">
+      <c r="B70" s="2" t="n">
         <v>45900</v>
       </c>
-      <c r="C70" s="1" t="n">
+      <c r="C70" s="2" t="n">
         <v>45931</v>
       </c>
       <c r="D70" t="inlineStr">
@@ -10456,7 +10468,7 @@
       <c r="I70" t="n">
         <v>1.95</v>
       </c>
-      <c r="J70" s="1" t="n">
+      <c r="J70" s="2" t="n">
         <v>45931</v>
       </c>
       <c r="K70" t="n">
@@ -10469,13 +10481,13 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>45901</v>
       </c>
-      <c r="B71" s="1" t="n">
+      <c r="B71" s="2" t="n">
         <v>45991</v>
       </c>
-      <c r="C71" s="1" t="n">
+      <c r="C71" s="2" t="n">
         <v>46021</v>
       </c>
       <c r="D71" t="inlineStr">
@@ -10502,7 +10514,7 @@
       <c r="I71" t="n">
         <v>1.7</v>
       </c>
-      <c r="J71" s="1" t="n">
+      <c r="J71" s="2" t="n">
         <v>46021</v>
       </c>
       <c r="K71" t="n">
@@ -10515,13 +10527,13 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>45992</v>
       </c>
-      <c r="B72" s="1" t="n">
+      <c r="B72" s="2" t="n">
         <v>46081</v>
       </c>
-      <c r="C72" s="1" t="n">
+      <c r="C72" s="2" t="n">
         <v>46113</v>
       </c>
       <c r="D72" t="inlineStr">
@@ -10548,7 +10560,7 @@
       <c r="I72" t="n">
         <v>1.51</v>
       </c>
-      <c r="J72" s="1" t="n">
+      <c r="J72" s="2" t="n">
         <v>46113</v>
       </c>
       <c r="K72" t="n">
@@ -10561,13 +10573,13 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>46082</v>
       </c>
-      <c r="B73" s="1" t="n">
+      <c r="B73" s="2" t="n">
         <v>46173</v>
       </c>
-      <c r="C73" s="1" t="n">
+      <c r="C73" s="2" t="n">
         <v>46218</v>
       </c>
       <c r="D73" t="inlineStr">
@@ -10594,7 +10606,7 @@
       <c r="I73" t="n">
         <v>2.1</v>
       </c>
-      <c r="J73" s="1" t="n">
+      <c r="J73" s="2" t="n">
         <v>46218</v>
       </c>
       <c r="K73" t="n">
@@ -10632,57 +10644,57 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>acciones</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>origen</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>40056</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>40094</v>
       </c>
       <c r="C2" t="n">
@@ -10712,10 +10724,10 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>40147</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>40184</v>
       </c>
       <c r="C3" t="n">
@@ -10745,10 +10757,10 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>40268</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>40275</v>
       </c>
       <c r="C4" t="n">
@@ -10778,10 +10790,10 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>40056</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>40457</v>
       </c>
       <c r="C5" t="n">
@@ -10815,10 +10827,10 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>40421</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>40457</v>
       </c>
       <c r="C6" t="n">
@@ -10852,10 +10864,10 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>40147</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>40549</v>
       </c>
       <c r="C7" t="n">
@@ -10889,10 +10901,10 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>40512</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>40549</v>
       </c>
       <c r="C8" t="n">
@@ -10926,10 +10938,10 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>40237</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>40639</v>
       </c>
       <c r="C9" t="n">
@@ -10963,10 +10975,10 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>40602</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>40639</v>
       </c>
       <c r="C10" t="n">
@@ -11000,10 +11012,10 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>39964</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>40746</v>
       </c>
       <c r="C11" t="n">
@@ -11037,10 +11049,10 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>40694</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>40746</v>
       </c>
       <c r="C12" t="n">
@@ -11074,10 +11086,10 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>40329</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>40746</v>
       </c>
       <c r="C13" t="n">
@@ -11111,10 +11123,10 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>40786</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>40822</v>
       </c>
       <c r="C14" t="n">
@@ -11148,10 +11160,10 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>40877</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>40913</v>
       </c>
       <c r="C15" t="n">
@@ -11185,10 +11197,10 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>40968</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>41005</v>
       </c>
       <c r="C16" t="n">
@@ -11222,10 +11234,10 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>41060</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>41114</v>
       </c>
       <c r="C17" t="n">
@@ -11259,10 +11271,10 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>41152</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>41191</v>
       </c>
       <c r="C18" t="n">
@@ -11296,10 +11308,10 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>41243</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>41283</v>
       </c>
       <c r="C19" t="n">
@@ -11333,10 +11345,10 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>41333</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>41368</v>
       </c>
       <c r="C20" t="n">
@@ -11370,10 +11382,10 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>41425</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>41478</v>
       </c>
       <c r="C21" t="n">
@@ -11407,10 +11419,10 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>41517</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>41554</v>
       </c>
       <c r="C22" t="n">
@@ -11444,10 +11456,10 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>41608</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>41646</v>
       </c>
       <c r="C23" t="n">
@@ -11481,10 +11493,10 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>41698</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>41736</v>
       </c>
       <c r="C24" t="n">
@@ -11518,10 +11530,10 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>41790</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>41845</v>
       </c>
       <c r="C25" t="n">
@@ -11555,10 +11567,10 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>41882</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>41919</v>
       </c>
       <c r="C26" t="n">
@@ -11592,10 +11604,10 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>41973</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>42011</v>
       </c>
       <c r="C27" t="n">
@@ -11629,10 +11641,10 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>42063</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>42101</v>
       </c>
       <c r="C28" t="n">
@@ -11666,10 +11678,10 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>42155</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>42208</v>
       </c>
       <c r="C29" t="n">
@@ -11703,10 +11715,10 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>42247</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>42283</v>
       </c>
       <c r="C30" t="n">
@@ -11740,10 +11752,10 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>42338</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>42375</v>
       </c>
       <c r="C31" t="n">
@@ -11777,10 +11789,10 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>42429</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>42465</v>
       </c>
       <c r="C32" t="n">
@@ -11814,10 +11826,10 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>42521</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>42572</v>
       </c>
       <c r="C33" t="n">
@@ -11851,10 +11863,10 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>42613</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>42654</v>
       </c>
       <c r="C34" t="n">
@@ -11888,10 +11900,10 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>42704</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>42740</v>
       </c>
       <c r="C35" t="n">
@@ -11925,10 +11937,10 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>42794</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>42829</v>
       </c>
       <c r="C36" t="n">
@@ -11962,10 +11974,10 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>42886</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>42936</v>
       </c>
       <c r="C37" t="n">
@@ -11999,10 +12011,10 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>42978</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>43014</v>
       </c>
       <c r="C38" t="n">
@@ -12036,10 +12048,10 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>43069</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>43105</v>
       </c>
       <c r="C39" t="n">
@@ -12073,10 +12085,10 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>43159</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>43195</v>
       </c>
       <c r="C40" t="n">
@@ -12110,10 +12122,10 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>43251</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>43306</v>
       </c>
       <c r="C41" t="n">
@@ -12147,10 +12159,10 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>43343</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>43378</v>
       </c>
       <c r="C42" t="n">
@@ -12184,10 +12196,10 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>43434</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>43473</v>
       </c>
       <c r="C43" t="n">
@@ -12221,10 +12233,10 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>43524</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>43559</v>
       </c>
       <c r="C44" t="n">
@@ -12258,10 +12270,10 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>43616</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>43669</v>
       </c>
       <c r="C45" t="n">
@@ -12295,10 +12307,10 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>43708</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>43742</v>
       </c>
       <c r="C46" t="n">
@@ -12332,10 +12344,10 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>43799</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>43837</v>
       </c>
       <c r="C47" t="n">
@@ -12369,10 +12381,10 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>43890</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>43928</v>
       </c>
       <c r="C48" t="n">
@@ -12406,10 +12418,10 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>43982</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>44036</v>
       </c>
       <c r="C49" t="n">
@@ -12443,10 +12455,10 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>44074</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>44112</v>
       </c>
       <c r="C50" t="n">
@@ -12480,10 +12492,10 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>44165</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>44201</v>
       </c>
       <c r="C51" t="n">
@@ -12517,10 +12529,10 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>44255</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>44288</v>
       </c>
       <c r="C52" t="n">
@@ -12554,10 +12566,10 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>44347</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>44397</v>
       </c>
       <c r="C53" t="n">
@@ -12591,10 +12603,10 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>44439</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>44474</v>
       </c>
       <c r="C54" t="n">
@@ -12628,10 +12640,10 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>44530</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>44567</v>
       </c>
       <c r="C55" t="n">
@@ -12665,10 +12677,10 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>44620</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>44656</v>
       </c>
       <c r="C56" t="n">
@@ -12702,10 +12714,10 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>44712</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="2" t="n">
         <v>44763</v>
       </c>
       <c r="C57" t="n">
@@ -12739,10 +12751,10 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>44804</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="2" t="n">
         <v>44840</v>
       </c>
       <c r="C58" t="n">
@@ -12776,10 +12788,10 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>44895</v>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="2" t="n">
         <v>44931</v>
       </c>
       <c r="C59" t="n">
@@ -12813,10 +12825,10 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>44985</v>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="2" t="n">
         <v>45022</v>
       </c>
       <c r="C60" t="n">
@@ -12850,10 +12862,10 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>45077</v>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="2" t="n">
         <v>45127</v>
       </c>
       <c r="C61" t="n">
@@ -12887,10 +12899,10 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>45169</v>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="2" t="n">
         <v>45205</v>
       </c>
       <c r="C62" t="n">
@@ -12924,10 +12936,10 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>45260</v>
       </c>
-      <c r="B63" s="1" t="n">
+      <c r="B63" s="2" t="n">
         <v>45296</v>
       </c>
       <c r="C63" t="n">
@@ -12961,10 +12973,10 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>45351</v>
       </c>
-      <c r="B64" s="1" t="n">
+      <c r="B64" s="2" t="n">
         <v>45386</v>
       </c>
       <c r="C64" t="n">
@@ -12998,10 +13010,10 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>45443</v>
       </c>
-      <c r="B65" s="1" t="n">
+      <c r="B65" s="2" t="n">
         <v>45498</v>
       </c>
       <c r="C65" t="n">
@@ -13035,10 +13047,10 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>45535</v>
       </c>
-      <c r="B66" s="1" t="n">
+      <c r="B66" s="2" t="n">
         <v>45572</v>
       </c>
       <c r="C66" t="n">
@@ -13072,10 +13084,10 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>45626</v>
       </c>
-      <c r="B67" s="1" t="n">
+      <c r="B67" s="2" t="n">
         <v>45660</v>
       </c>
       <c r="C67" t="n">
@@ -13109,10 +13121,10 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>45716</v>
       </c>
-      <c r="B68" s="1" t="n">
+      <c r="B68" s="2" t="n">
         <v>45750</v>
       </c>
       <c r="C68" t="n">
@@ -13146,10 +13158,10 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>45808</v>
       </c>
-      <c r="B69" s="1" t="n">
+      <c r="B69" s="2" t="n">
         <v>45855</v>
       </c>
       <c r="C69" t="n">
@@ -13183,10 +13195,10 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>45900</v>
       </c>
-      <c r="B70" s="1" t="n">
+      <c r="B70" s="2" t="n">
         <v>45931</v>
       </c>
       <c r="C70" t="n">
@@ -13220,10 +13232,10 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>45991</v>
       </c>
-      <c r="B71" s="1" t="n">
+      <c r="B71" s="2" t="n">
         <v>46021</v>
       </c>
       <c r="C71" t="n">
@@ -13257,10 +13269,10 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>46081</v>
       </c>
-      <c r="B72" s="1" t="n">
+      <c r="B72" s="2" t="n">
         <v>46113</v>
       </c>
       <c r="C72" t="n">
@@ -13294,10 +13306,10 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>46173</v>
       </c>
-      <c r="B73" s="1" t="n">
+      <c r="B73" s="2" t="n">
         <v>46218</v>
       </c>
       <c r="C73" t="n">
@@ -13349,12 +13361,12 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>campo</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>valor</t>
         </is>

--- a/salidas/empresas/NKE.xlsx
+++ b/salidas/empresas/NKE.xlsx
@@ -498,7 +498,7 @@
         <v>38748</v>
       </c>
       <c r="B2" t="n">
-        <v>7.582486152648926</v>
+        <v>7.5824875831604</v>
       </c>
       <c r="C2" t="n">
         <v>10.11874961853027</v>
@@ -517,7 +517,7 @@
         <v>38776</v>
       </c>
       <c r="B3" t="n">
-        <v>8.128575325012207</v>
+        <v>8.128569602966309</v>
       </c>
       <c r="C3" t="n">
         <v>10.84749984741211</v>
@@ -536,7 +536,7 @@
         <v>38807</v>
       </c>
       <c r="B4" t="n">
-        <v>7.985776901245117</v>
+        <v>7.985780239105225</v>
       </c>
       <c r="C4" t="n">
         <v>10.63749980926514</v>
@@ -555,7 +555,7 @@
         <v>38837</v>
       </c>
       <c r="B5" t="n">
-        <v>7.67986011505127</v>
+        <v>7.679855346679688</v>
       </c>
       <c r="C5" t="n">
         <v>10.22999954223633</v>
@@ -574,7 +574,7 @@
         <v>38868</v>
       </c>
       <c r="B6" t="n">
-        <v>7.536279201507568</v>
+        <v>7.536284446716309</v>
       </c>
       <c r="C6" t="n">
         <v>10.03874969482422</v>
@@ -593,7 +593,7 @@
         <v>38898</v>
       </c>
       <c r="B7" t="n">
-        <v>7.615654945373535</v>
+        <v>7.615651607513428</v>
       </c>
       <c r="C7" t="n">
         <v>10.125</v>
@@ -612,7 +612,7 @@
         <v>38929</v>
       </c>
       <c r="B8" t="n">
-        <v>7.427614688873291</v>
+        <v>7.427608966827393</v>
       </c>
       <c r="C8" t="n">
         <v>9.875</v>
@@ -631,7 +631,7 @@
         <v>38960</v>
       </c>
       <c r="B9" t="n">
-        <v>7.593087196350098</v>
+        <v>7.593090534210205</v>
       </c>
       <c r="C9" t="n">
         <v>10.09500026702881</v>
@@ -650,7 +650,7 @@
         <v>38990</v>
       </c>
       <c r="B10" t="n">
-        <v>8.25386905670166</v>
+        <v>8.253866195678711</v>
       </c>
       <c r="C10" t="n">
         <v>10.95250034332275</v>
@@ -669,7 +669,7 @@
         <v>39021</v>
       </c>
       <c r="B11" t="n">
-        <v>8.65516185760498</v>
+        <v>8.65516471862793</v>
       </c>
       <c r="C11" t="n">
         <v>11.48499965667725</v>
@@ -688,7 +688,7 @@
         <v>39051</v>
       </c>
       <c r="B12" t="n">
-        <v>9.321163177490234</v>
+        <v>9.321159362792969</v>
       </c>
       <c r="C12" t="n">
         <v>12.36874961853027</v>
@@ -707,7 +707,7 @@
         <v>39082</v>
       </c>
       <c r="B13" t="n">
-        <v>9.346307754516602</v>
+        <v>9.34630298614502</v>
       </c>
       <c r="C13" t="n">
         <v>12.37874984741211</v>
@@ -726,7 +726,7 @@
         <v>39113</v>
       </c>
       <c r="B14" t="n">
-        <v>9.325542449951172</v>
+        <v>9.325541496276855</v>
       </c>
       <c r="C14" t="n">
         <v>12.35124969482422</v>
@@ -745,7 +745,7 @@
         <v>39141</v>
       </c>
       <c r="B15" t="n">
-        <v>9.859724044799805</v>
+        <v>9.859728813171387</v>
       </c>
       <c r="C15" t="n">
         <v>13.05875015258789</v>
@@ -764,7 +764,7 @@
         <v>39172</v>
       </c>
       <c r="B16" t="n">
-        <v>10.04642963409424</v>
+        <v>10.04643726348877</v>
       </c>
       <c r="C16" t="n">
         <v>13.28250026702881</v>
@@ -783,7 +783,7 @@
         <v>39202</v>
       </c>
       <c r="B17" t="n">
-        <v>10.18446731567383</v>
+        <v>10.18447303771973</v>
       </c>
       <c r="C17" t="n">
         <v>13.46500015258789</v>
@@ -802,7 +802,7 @@
         <v>39233</v>
       </c>
       <c r="B18" t="n">
-        <v>10.73094272613525</v>
+        <v>10.7309455871582</v>
       </c>
       <c r="C18" t="n">
         <v>14.1875</v>
@@ -821,7 +821,7 @@
         <v>39263</v>
       </c>
       <c r="B19" t="n">
-        <v>11.05886840820312</v>
+        <v>11.05886650085449</v>
       </c>
       <c r="C19" t="n">
         <v>14.57250022888184</v>
@@ -840,7 +840,7 @@
         <v>39294</v>
       </c>
       <c r="B20" t="n">
-        <v>10.70978164672852</v>
+        <v>10.70978260040283</v>
       </c>
       <c r="C20" t="n">
         <v>14.11250019073486</v>
@@ -878,7 +878,7 @@
         <v>39355</v>
       </c>
       <c r="B22" t="n">
-        <v>11.16630458831787</v>
+        <v>11.1663064956665</v>
       </c>
       <c r="C22" t="n">
         <v>14.66499996185303</v>
@@ -897,7 +897,7 @@
         <v>39386</v>
       </c>
       <c r="B23" t="n">
-        <v>12.61301326751709</v>
+        <v>12.61301517486572</v>
       </c>
       <c r="C23" t="n">
         <v>16.56500053405762</v>
@@ -916,7 +916,7 @@
         <v>39416</v>
       </c>
       <c r="B24" t="n">
-        <v>12.49689960479736</v>
+        <v>12.49689865112305</v>
       </c>
       <c r="C24" t="n">
         <v>16.41250038146973</v>
@@ -935,7 +935,7 @@
         <v>39447</v>
       </c>
       <c r="B25" t="n">
-        <v>12.2712984085083</v>
+        <v>12.27129554748535</v>
       </c>
       <c r="C25" t="n">
         <v>16.05999946594238</v>
@@ -954,7 +954,7 @@
         <v>39478</v>
       </c>
       <c r="B26" t="n">
-        <v>11.71542453765869</v>
+        <v>11.71542358398438</v>
       </c>
       <c r="C26" t="n">
         <v>15.33250045776367</v>
@@ -973,7 +973,7 @@
         <v>39507</v>
       </c>
       <c r="B27" t="n">
-        <v>11.49957084655762</v>
+        <v>11.49956512451172</v>
       </c>
       <c r="C27" t="n">
         <v>15.05000019073486</v>
@@ -992,7 +992,7 @@
         <v>39538</v>
       </c>
       <c r="B28" t="n">
-        <v>13.03886032104492</v>
+        <v>13.03885936737061</v>
       </c>
       <c r="C28" t="n">
         <v>17</v>
@@ -1011,7 +1011,7 @@
         <v>39568</v>
       </c>
       <c r="B29" t="n">
-        <v>12.808762550354</v>
+        <v>12.80876541137695</v>
       </c>
       <c r="C29" t="n">
         <v>16.70000076293945</v>
@@ -1030,7 +1030,7 @@
         <v>39599</v>
       </c>
       <c r="B30" t="n">
-        <v>13.10980319976807</v>
+        <v>13.10980987548828</v>
       </c>
       <c r="C30" t="n">
         <v>17.09250068664551</v>
@@ -1049,7 +1049,7 @@
         <v>39629</v>
       </c>
       <c r="B31" t="n">
-        <v>11.46891784667969</v>
+        <v>11.46892261505127</v>
       </c>
       <c r="C31" t="n">
         <v>14.90250015258789</v>
@@ -1068,7 +1068,7 @@
         <v>39660</v>
       </c>
       <c r="B32" t="n">
-        <v>11.28998851776123</v>
+        <v>11.28998947143555</v>
       </c>
       <c r="C32" t="n">
         <v>14.67000007629395</v>
@@ -1087,7 +1087,7 @@
         <v>39691</v>
       </c>
       <c r="B33" t="n">
-        <v>11.66132068634033</v>
+        <v>11.66131973266602</v>
       </c>
       <c r="C33" t="n">
         <v>15.15250015258789</v>
@@ -1106,7 +1106,7 @@
         <v>39721</v>
       </c>
       <c r="B34" t="n">
-        <v>12.91950798034668</v>
+        <v>12.91951370239258</v>
       </c>
       <c r="C34" t="n">
         <v>16.72500038146973</v>
@@ -1125,7 +1125,7 @@
         <v>39752</v>
       </c>
       <c r="B35" t="n">
-        <v>11.12931632995605</v>
+        <v>11.12931728363037</v>
       </c>
       <c r="C35" t="n">
         <v>14.40750026702881</v>
@@ -1144,7 +1144,7 @@
         <v>39782</v>
       </c>
       <c r="B36" t="n">
-        <v>10.28346824645996</v>
+        <v>10.28346538543701</v>
       </c>
       <c r="C36" t="n">
         <v>13.3125</v>
@@ -1163,7 +1163,7 @@
         <v>39813</v>
       </c>
       <c r="B37" t="n">
-        <v>9.896522521972656</v>
+        <v>9.896520614624023</v>
       </c>
       <c r="C37" t="n">
         <v>12.75</v>
@@ -1182,7 +1182,7 @@
         <v>39844</v>
       </c>
       <c r="B38" t="n">
-        <v>8.780738830566406</v>
+        <v>8.780735969543457</v>
       </c>
       <c r="C38" t="n">
         <v>11.3125</v>
@@ -1201,7 +1201,7 @@
         <v>39872</v>
       </c>
       <c r="B39" t="n">
-        <v>8.058873176574707</v>
+        <v>8.05887508392334</v>
       </c>
       <c r="C39" t="n">
         <v>10.38249969482422</v>
@@ -1239,7 +1239,7 @@
         <v>39933</v>
       </c>
       <c r="B41" t="n">
-        <v>10.24195003509521</v>
+        <v>10.24195384979248</v>
       </c>
       <c r="C41" t="n">
         <v>13.11750030517578</v>
@@ -1258,7 +1258,7 @@
         <v>39964</v>
       </c>
       <c r="B42" t="n">
-        <v>11.13595104217529</v>
+        <v>11.13594818115234</v>
       </c>
       <c r="C42" t="n">
         <v>14.26249980926514</v>
@@ -1277,7 +1277,7 @@
         <v>39994</v>
       </c>
       <c r="B43" t="n">
-        <v>10.15089321136475</v>
+        <v>10.1508960723877</v>
       </c>
       <c r="C43" t="n">
         <v>12.94499969482422</v>
@@ -1296,7 +1296,7 @@
         <v>40025</v>
       </c>
       <c r="B44" t="n">
-        <v>11.10363960266113</v>
+        <v>11.1036376953125</v>
       </c>
       <c r="C44" t="n">
         <v>14.15999984741211</v>
@@ -1315,7 +1315,7 @@
         <v>40056</v>
       </c>
       <c r="B45" t="n">
-        <v>10.85859203338623</v>
+        <v>10.85859298706055</v>
       </c>
       <c r="C45" t="n">
         <v>13.84749984741211</v>
@@ -1334,7 +1334,7 @@
         <v>40086</v>
       </c>
       <c r="B46" t="n">
-        <v>12.74346923828125</v>
+        <v>12.74347114562988</v>
       </c>
       <c r="C46" t="n">
         <v>16.17499923706055</v>
@@ -1353,7 +1353,7 @@
         <v>40117</v>
       </c>
       <c r="B47" t="n">
-        <v>12.24712944030762</v>
+        <v>12.24713325500488</v>
       </c>
       <c r="C47" t="n">
         <v>15.54500007629395</v>
@@ -1378,7 +1378,7 @@
         <v>40147</v>
       </c>
       <c r="B48" t="n">
-        <v>12.78089904785156</v>
+        <v>12.78090000152588</v>
       </c>
       <c r="C48" t="n">
         <v>16.22249984741211</v>
@@ -1403,7 +1403,7 @@
         <v>40178</v>
       </c>
       <c r="B49" t="n">
-        <v>13.06730175018311</v>
+        <v>13.06730651855469</v>
       </c>
       <c r="C49" t="n">
         <v>16.51749992370605</v>
@@ -1428,7 +1428,7 @@
         <v>40209</v>
       </c>
       <c r="B50" t="n">
-        <v>12.60844898223877</v>
+        <v>12.60845470428467</v>
       </c>
       <c r="C50" t="n">
         <v>15.9375</v>
@@ -1453,7 +1453,7 @@
         <v>40237</v>
       </c>
       <c r="B51" t="n">
-        <v>13.36990642547607</v>
+        <v>13.36990737915039</v>
       </c>
       <c r="C51" t="n">
         <v>16.89999961853027</v>
@@ -1503,7 +1503,7 @@
         <v>40298</v>
       </c>
       <c r="B53" t="n">
-        <v>15.07362747192383</v>
+        <v>15.07362365722656</v>
       </c>
       <c r="C53" t="n">
         <v>18.97750091552734</v>
@@ -1528,7 +1528,7 @@
         <v>40329</v>
       </c>
       <c r="B54" t="n">
-        <v>14.37266540527344</v>
+        <v>14.3726634979248</v>
       </c>
       <c r="C54" t="n">
         <v>18.09499931335449</v>
@@ -1553,7 +1553,7 @@
         <v>40359</v>
       </c>
       <c r="B55" t="n">
-        <v>13.46335983276367</v>
+        <v>13.46335506439209</v>
       </c>
       <c r="C55" t="n">
         <v>16.88750076293945</v>
@@ -1578,7 +1578,7 @@
         <v>40390</v>
       </c>
       <c r="B56" t="n">
-        <v>14.67715358734131</v>
+        <v>14.67714595794678</v>
       </c>
       <c r="C56" t="n">
         <v>18.40999984741211</v>
@@ -1607,7 +1607,7 @@
         <v>40421</v>
       </c>
       <c r="B57" t="n">
-        <v>13.95166301727295</v>
+        <v>13.95166492462158</v>
       </c>
       <c r="C57" t="n">
         <v>17.5</v>
@@ -1636,7 +1636,7 @@
         <v>40451</v>
       </c>
       <c r="B58" t="n">
-        <v>16.03267478942871</v>
+        <v>16.03267860412598</v>
       </c>
       <c r="C58" t="n">
         <v>20.03499984741211</v>
@@ -1665,7 +1665,7 @@
         <v>40482</v>
       </c>
       <c r="B59" t="n">
-        <v>16.29275512695312</v>
+        <v>16.29275703430176</v>
       </c>
       <c r="C59" t="n">
         <v>20.36000061035156</v>
@@ -1694,7 +1694,7 @@
         <v>40512</v>
       </c>
       <c r="B60" t="n">
-        <v>17.23101806640625</v>
+        <v>17.23101997375488</v>
       </c>
       <c r="C60" t="n">
         <v>21.53249931335449</v>
@@ -1723,7 +1723,7 @@
         <v>40543</v>
       </c>
       <c r="B61" t="n">
-        <v>17.1496467590332</v>
+        <v>17.14965057373047</v>
       </c>
       <c r="C61" t="n">
         <v>21.35499954223633</v>
@@ -1752,7 +1752,7 @@
         <v>40574</v>
       </c>
       <c r="B62" t="n">
-        <v>16.55939102172852</v>
+        <v>16.55938720703125</v>
       </c>
       <c r="C62" t="n">
         <v>20.6200008392334</v>
@@ -1781,7 +1781,7 @@
         <v>40602</v>
       </c>
       <c r="B63" t="n">
-        <v>17.87442016601562</v>
+        <v>17.87441635131836</v>
       </c>
       <c r="C63" t="n">
         <v>22.25749969482422</v>
@@ -1810,7 +1810,7 @@
         <v>40633</v>
       </c>
       <c r="B64" t="n">
-        <v>15.25169563293457</v>
+        <v>15.25170516967773</v>
       </c>
       <c r="C64" t="n">
         <v>18.92499923706055</v>
@@ -1839,7 +1839,7 @@
         <v>40663</v>
       </c>
       <c r="B65" t="n">
-        <v>16.58547019958496</v>
+        <v>16.58547782897949</v>
       </c>
       <c r="C65" t="n">
         <v>20.57999992370605</v>
@@ -1868,7 +1868,7 @@
         <v>40694</v>
       </c>
       <c r="B66" t="n">
-        <v>17.01460647583008</v>
+        <v>17.01461219787598</v>
       </c>
       <c r="C66" t="n">
         <v>21.11249923706055</v>
@@ -1897,7 +1897,7 @@
         <v>40724</v>
       </c>
       <c r="B67" t="n">
-        <v>18.19744110107422</v>
+        <v>18.19744873046875</v>
       </c>
       <c r="C67" t="n">
         <v>22.4950008392334</v>
@@ -1926,7 +1926,7 @@
         <v>40755</v>
       </c>
       <c r="B68" t="n">
-        <v>18.2318229675293</v>
+        <v>18.23182678222656</v>
       </c>
       <c r="C68" t="n">
         <v>22.53750038146973</v>
@@ -1955,7 +1955,7 @@
         <v>40786</v>
       </c>
       <c r="B69" t="n">
-        <v>17.52398872375488</v>
+        <v>17.52399063110352</v>
       </c>
       <c r="C69" t="n">
         <v>21.66250038146973</v>
@@ -2013,7 +2013,7 @@
         <v>40847</v>
       </c>
       <c r="B71" t="n">
-        <v>19.55566024780273</v>
+        <v>19.5556697845459</v>
       </c>
       <c r="C71" t="n">
         <v>24.08749961853027</v>
@@ -2042,7 +2042,7 @@
         <v>40877</v>
       </c>
       <c r="B72" t="n">
-        <v>19.52116203308105</v>
+        <v>19.52116775512695</v>
       </c>
       <c r="C72" t="n">
         <v>24.04500007629395</v>
@@ -2071,7 +2071,7 @@
         <v>40908</v>
       </c>
       <c r="B73" t="n">
-        <v>19.63321495056152</v>
+        <v>19.63321113586426</v>
       </c>
       <c r="C73" t="n">
         <v>24.09250068664551</v>
@@ -2129,7 +2129,7 @@
         <v>40968</v>
       </c>
       <c r="B75" t="n">
-        <v>21.98626327514648</v>
+        <v>21.98626899719238</v>
       </c>
       <c r="C75" t="n">
         <v>26.97999954223633</v>
@@ -2158,7 +2158,7 @@
         <v>40999</v>
       </c>
       <c r="B76" t="n">
-        <v>22.16615104675293</v>
+        <v>22.16614723205566</v>
       </c>
       <c r="C76" t="n">
         <v>27.11000061035156</v>
@@ -2187,7 +2187,7 @@
         <v>41029</v>
       </c>
       <c r="B77" t="n">
-        <v>22.86726951599121</v>
+        <v>22.86727523803711</v>
       </c>
       <c r="C77" t="n">
         <v>27.96750068664551</v>
@@ -2216,7 +2216,7 @@
         <v>41060</v>
       </c>
       <c r="B78" t="n">
-        <v>22.18653678894043</v>
+        <v>22.18654251098633</v>
       </c>
       <c r="C78" t="n">
         <v>27.04500007629395</v>
@@ -2245,7 +2245,7 @@
         <v>41090</v>
       </c>
       <c r="B79" t="n">
-        <v>18.00271987915039</v>
+        <v>18.00272369384766</v>
       </c>
       <c r="C79" t="n">
         <v>21.94499969482422</v>
@@ -2274,7 +2274,7 @@
         <v>41121</v>
       </c>
       <c r="B80" t="n">
-        <v>19.14506530761719</v>
+        <v>19.14506912231445</v>
       </c>
       <c r="C80" t="n">
         <v>23.33749961853027</v>
@@ -2303,7 +2303,7 @@
         <v>41152</v>
       </c>
       <c r="B81" t="n">
-        <v>20.04058074951172</v>
+        <v>20.04057884216309</v>
       </c>
       <c r="C81" t="n">
         <v>24.34000015258789</v>
@@ -2332,7 +2332,7 @@
         <v>41182</v>
       </c>
       <c r="B82" t="n">
-        <v>19.53627395629883</v>
+        <v>19.53627586364746</v>
       </c>
       <c r="C82" t="n">
         <v>23.72750091552734</v>
@@ -2361,7 +2361,7 @@
         <v>41213</v>
       </c>
       <c r="B83" t="n">
-        <v>18.80965995788574</v>
+        <v>18.80965423583984</v>
       </c>
       <c r="C83" t="n">
         <v>22.84499931335449</v>
@@ -2390,7 +2390,7 @@
         <v>41243</v>
       </c>
       <c r="B84" t="n">
-        <v>20.06528663635254</v>
+        <v>20.06528472900391</v>
       </c>
       <c r="C84" t="n">
         <v>24.3700008392334</v>
@@ -2419,7 +2419,7 @@
         <v>41274</v>
       </c>
       <c r="B85" t="n">
-        <v>21.33441925048828</v>
+        <v>21.33441734313965</v>
       </c>
       <c r="C85" t="n">
         <v>25.79999923706055</v>
@@ -2448,7 +2448,7 @@
         <v>41305</v>
       </c>
       <c r="B86" t="n">
-        <v>22.34738922119141</v>
+        <v>22.34738731384277</v>
       </c>
       <c r="C86" t="n">
         <v>27.02499961853027</v>
@@ -2506,7 +2506,7 @@
         <v>41364</v>
       </c>
       <c r="B88" t="n">
-        <v>24.49279403686523</v>
+        <v>24.49279594421387</v>
       </c>
       <c r="C88" t="n">
         <v>29.5049991607666</v>
@@ -2535,7 +2535,7 @@
         <v>41394</v>
       </c>
       <c r="B89" t="n">
-        <v>26.39792823791504</v>
+        <v>26.3979320526123</v>
       </c>
       <c r="C89" t="n">
         <v>31.79999923706055</v>
@@ -2564,7 +2564,7 @@
         <v>41425</v>
       </c>
       <c r="B90" t="n">
-        <v>25.67839241027832</v>
+        <v>25.67839050292969</v>
       </c>
       <c r="C90" t="n">
         <v>30.82999992370605</v>
@@ -2593,7 +2593,7 @@
         <v>41455</v>
       </c>
       <c r="B91" t="n">
-        <v>26.51963233947754</v>
+        <v>26.51962471008301</v>
       </c>
       <c r="C91" t="n">
         <v>31.84000015258789</v>
@@ -2622,7 +2622,7 @@
         <v>41486</v>
       </c>
       <c r="B92" t="n">
-        <v>26.20312881469727</v>
+        <v>26.20312118530273</v>
       </c>
       <c r="C92" t="n">
         <v>31.45999908447266</v>
@@ -2680,7 +2680,7 @@
         <v>41547</v>
       </c>
       <c r="B94" t="n">
-        <v>30.35161399841309</v>
+        <v>30.35162162780762</v>
       </c>
       <c r="C94" t="n">
         <v>36.31999969482422</v>
@@ -2709,7 +2709,7 @@
         <v>41578</v>
       </c>
       <c r="B95" t="n">
-        <v>31.6552677154541</v>
+        <v>31.65526008605957</v>
       </c>
       <c r="C95" t="n">
         <v>37.88000106811523</v>
@@ -2738,7 +2738,7 @@
         <v>41608</v>
       </c>
       <c r="B96" t="n">
-        <v>33.06755065917969</v>
+        <v>33.06755447387695</v>
       </c>
       <c r="C96" t="n">
         <v>39.56999969482422</v>
@@ -2796,7 +2796,7 @@
         <v>41670</v>
       </c>
       <c r="B98" t="n">
-        <v>30.53472709655762</v>
+        <v>30.53473854064941</v>
       </c>
       <c r="C98" t="n">
         <v>36.42499923706055</v>
@@ -2825,7 +2825,7 @@
         <v>41698</v>
       </c>
       <c r="B99" t="n">
-        <v>32.91981887817383</v>
+        <v>32.91982269287109</v>
       </c>
       <c r="C99" t="n">
         <v>39.15000152587891</v>
@@ -2854,7 +2854,7 @@
         <v>41729</v>
       </c>
       <c r="B100" t="n">
-        <v>31.0531177520752</v>
+        <v>31.05311012268066</v>
       </c>
       <c r="C100" t="n">
         <v>36.93000030517578</v>
@@ -2883,7 +2883,7 @@
         <v>41759</v>
       </c>
       <c r="B101" t="n">
-        <v>30.67050361633301</v>
+        <v>30.67051124572754</v>
       </c>
       <c r="C101" t="n">
         <v>36.47499847412109</v>
@@ -2912,7 +2912,7 @@
         <v>41790</v>
       </c>
       <c r="B102" t="n">
-        <v>32.43750381469727</v>
+        <v>32.43749618530273</v>
       </c>
       <c r="C102" t="n">
         <v>38.45500183105469</v>
@@ -2941,7 +2941,7 @@
         <v>41820</v>
       </c>
       <c r="B103" t="n">
-        <v>32.70743560791016</v>
+        <v>32.70741653442383</v>
       </c>
       <c r="C103" t="n">
         <v>38.77500152587891</v>
@@ -2970,7 +2970,7 @@
         <v>41851</v>
       </c>
       <c r="B104" t="n">
-        <v>32.53026962280273</v>
+        <v>32.5302848815918</v>
       </c>
       <c r="C104" t="n">
         <v>38.56499862670898</v>
@@ -2999,7 +2999,7 @@
         <v>41882</v>
       </c>
       <c r="B105" t="n">
-        <v>33.22922515869141</v>
+        <v>33.22921371459961</v>
       </c>
       <c r="C105" t="n">
         <v>39.27500152587891</v>
@@ -3028,7 +3028,7 @@
         <v>41912</v>
       </c>
       <c r="B106" t="n">
-        <v>37.73451614379883</v>
+        <v>37.73451995849609</v>
       </c>
       <c r="C106" t="n">
         <v>44.59999847412109</v>
@@ -3057,7 +3057,7 @@
         <v>41943</v>
       </c>
       <c r="B107" t="n">
-        <v>39.329345703125</v>
+        <v>39.32934188842773</v>
       </c>
       <c r="C107" t="n">
         <v>46.48500061035156</v>
@@ -3086,7 +3086,7 @@
         <v>41973</v>
       </c>
       <c r="B108" t="n">
-        <v>42.0029182434082</v>
+        <v>42.00291442871094</v>
       </c>
       <c r="C108" t="n">
         <v>49.64500045776367</v>
@@ -3115,7 +3115,7 @@
         <v>42004</v>
       </c>
       <c r="B109" t="n">
-        <v>40.79155349731445</v>
+        <v>40.79155731201172</v>
       </c>
       <c r="C109" t="n">
         <v>48.07500076293945</v>
@@ -3144,7 +3144,7 @@
         <v>42035</v>
       </c>
       <c r="B110" t="n">
-        <v>39.13697052001953</v>
+        <v>39.13698196411133</v>
       </c>
       <c r="C110" t="n">
         <v>46.125</v>
@@ -3202,7 +3202,7 @@
         <v>42094</v>
       </c>
       <c r="B112" t="n">
-        <v>42.68834686279297</v>
+        <v>42.68836975097656</v>
       </c>
       <c r="C112" t="n">
         <v>50.16500091552734</v>
@@ -3231,7 +3231,7 @@
         <v>42124</v>
       </c>
       <c r="B113" t="n">
-        <v>42.05440139770508</v>
+        <v>42.05439758300781</v>
       </c>
       <c r="C113" t="n">
         <v>49.41999816894531</v>
@@ -3289,7 +3289,7 @@
         <v>42185</v>
       </c>
       <c r="B115" t="n">
-        <v>46.08578109741211</v>
+        <v>46.08577346801758</v>
       </c>
       <c r="C115" t="n">
         <v>54.0099983215332</v>
@@ -3318,7 +3318,7 @@
         <v>42216</v>
       </c>
       <c r="B116" t="n">
-        <v>49.1575927734375</v>
+        <v>49.15759658813477</v>
       </c>
       <c r="C116" t="n">
         <v>57.61000061035156</v>
@@ -3347,7 +3347,7 @@
         <v>42247</v>
       </c>
       <c r="B117" t="n">
-        <v>47.67715454101562</v>
+        <v>47.67713928222656</v>
       </c>
       <c r="C117" t="n">
         <v>55.875</v>
@@ -3405,7 +3405,7 @@
         <v>42308</v>
       </c>
       <c r="B119" t="n">
-        <v>56.0445442199707</v>
+        <v>56.04454040527344</v>
       </c>
       <c r="C119" t="n">
         <v>65.51499938964844</v>
@@ -3434,7 +3434,7 @@
         <v>42338</v>
       </c>
       <c r="B120" t="n">
-        <v>56.57918548583984</v>
+        <v>56.57918930053711</v>
       </c>
       <c r="C120" t="n">
         <v>66.13999938964844</v>
@@ -3463,7 +3463,7 @@
         <v>42369</v>
       </c>
       <c r="B121" t="n">
-        <v>53.5949821472168</v>
+        <v>53.59497833251953</v>
       </c>
       <c r="C121" t="n">
         <v>62.5</v>
@@ -3492,7 +3492,7 @@
         <v>42400</v>
       </c>
       <c r="B122" t="n">
-        <v>53.1747932434082</v>
+        <v>53.17479705810547</v>
       </c>
       <c r="C122" t="n">
         <v>62.0099983215332</v>
@@ -3521,7 +3521,7 @@
         <v>42429</v>
       </c>
       <c r="B123" t="n">
-        <v>52.81463241577148</v>
+        <v>52.81464004516602</v>
       </c>
       <c r="C123" t="n">
         <v>61.59000015258789</v>
@@ -3550,7 +3550,7 @@
         <v>42460</v>
       </c>
       <c r="B124" t="n">
-        <v>52.84762954711914</v>
+        <v>52.84763336181641</v>
       </c>
       <c r="C124" t="n">
         <v>61.47000122070312</v>
@@ -3608,7 +3608,7 @@
         <v>42521</v>
       </c>
       <c r="B126" t="n">
-        <v>47.47432708740234</v>
+        <v>47.47431945800781</v>
       </c>
       <c r="C126" t="n">
         <v>55.22000122070312</v>
@@ -3637,7 +3637,7 @@
         <v>42551</v>
       </c>
       <c r="B127" t="n">
-        <v>47.59575653076172</v>
+        <v>47.59576797485352</v>
       </c>
       <c r="C127" t="n">
         <v>55.20000076293945</v>
@@ -3695,7 +3695,7 @@
         <v>42613</v>
       </c>
       <c r="B129" t="n">
-        <v>49.69962692260742</v>
+        <v>49.69962310791016</v>
       </c>
       <c r="C129" t="n">
         <v>57.63999938964844</v>
@@ -3724,7 +3724,7 @@
         <v>42643</v>
       </c>
       <c r="B130" t="n">
-        <v>45.52341461181641</v>
+        <v>45.52342224121094</v>
       </c>
       <c r="C130" t="n">
         <v>52.65000152587891</v>
@@ -3753,7 +3753,7 @@
         <v>42674</v>
       </c>
       <c r="B131" t="n">
-        <v>43.38775634765625</v>
+        <v>43.38774871826172</v>
       </c>
       <c r="C131" t="n">
         <v>50.18000030517578</v>
@@ -3782,7 +3782,7 @@
         <v>42704</v>
       </c>
       <c r="B132" t="n">
-        <v>43.29264068603516</v>
+        <v>43.29262924194336</v>
       </c>
       <c r="C132" t="n">
         <v>50.06999969482422</v>
@@ -3811,7 +3811,7 @@
         <v>42735</v>
       </c>
       <c r="B133" t="n">
-        <v>44.10834884643555</v>
+        <v>44.10834121704102</v>
       </c>
       <c r="C133" t="n">
         <v>50.83000183105469</v>
@@ -3869,7 +3869,7 @@
         <v>42794</v>
       </c>
       <c r="B135" t="n">
-        <v>49.60125732421875</v>
+        <v>49.60125350952148</v>
       </c>
       <c r="C135" t="n">
         <v>57.15999984741211</v>
@@ -3927,7 +3927,7 @@
         <v>42855</v>
       </c>
       <c r="B137" t="n">
-        <v>48.23250198364258</v>
+        <v>48.23248291015625</v>
       </c>
       <c r="C137" t="n">
         <v>55.40999984741211</v>
@@ -3985,7 +3985,7 @@
         <v>42916</v>
       </c>
       <c r="B139" t="n">
-        <v>51.53252792358398</v>
+        <v>51.53251647949219</v>
       </c>
       <c r="C139" t="n">
         <v>59</v>
@@ -4043,7 +4043,7 @@
         <v>42978</v>
       </c>
       <c r="B141" t="n">
-        <v>46.28446578979492</v>
+        <v>46.28448104858398</v>
       </c>
       <c r="C141" t="n">
         <v>52.81000137329102</v>
@@ -4072,7 +4072,7 @@
         <v>43008</v>
       </c>
       <c r="B142" t="n">
-        <v>45.4431037902832</v>
+        <v>45.44309616088867</v>
       </c>
       <c r="C142" t="n">
         <v>51.84999847412109</v>
@@ -4101,7 +4101,7 @@
         <v>43039</v>
       </c>
       <c r="B143" t="n">
-        <v>48.19509887695312</v>
+        <v>48.19510650634766</v>
       </c>
       <c r="C143" t="n">
         <v>54.9900016784668</v>
@@ -4130,7 +4130,7 @@
         <v>43069</v>
       </c>
       <c r="B144" t="n">
-        <v>52.95413589477539</v>
+        <v>52.95414352416992</v>
       </c>
       <c r="C144" t="n">
         <v>60.41999816894531</v>
@@ -4217,7 +4217,7 @@
         <v>43159</v>
       </c>
       <c r="B147" t="n">
-        <v>58.94247436523438</v>
+        <v>58.94247817993164</v>
       </c>
       <c r="C147" t="n">
         <v>67.02999877929688</v>
@@ -4246,7 +4246,7 @@
         <v>43190</v>
       </c>
       <c r="B148" t="n">
-        <v>58.60038375854492</v>
+        <v>58.60037994384766</v>
       </c>
       <c r="C148" t="n">
         <v>66.44000244140625</v>
@@ -4275,7 +4275,7 @@
         <v>43220</v>
       </c>
       <c r="B149" t="n">
-        <v>60.32028961181641</v>
+        <v>60.32028579711914</v>
       </c>
       <c r="C149" t="n">
         <v>68.38999938964844</v>
@@ -4304,7 +4304,7 @@
         <v>43251</v>
       </c>
       <c r="B150" t="n">
-        <v>63.32794189453125</v>
+        <v>63.32792663574219</v>
       </c>
       <c r="C150" t="n">
         <v>71.80000305175781</v>
@@ -4362,7 +4362,7 @@
         <v>43312</v>
       </c>
       <c r="B152" t="n">
-        <v>68.02445983886719</v>
+        <v>68.02446746826172</v>
       </c>
       <c r="C152" t="n">
         <v>76.91000366210938</v>
@@ -4391,7 +4391,7 @@
         <v>43343</v>
       </c>
       <c r="B153" t="n">
-        <v>72.88235473632812</v>
+        <v>72.88236236572266</v>
       </c>
       <c r="C153" t="n">
         <v>82.19999694824219</v>
@@ -4420,7 +4420,7 @@
         <v>43373</v>
       </c>
       <c r="B154" t="n">
-        <v>75.11672210693359</v>
+        <v>75.11671447753906</v>
       </c>
       <c r="C154" t="n">
         <v>84.72000122070312</v>
@@ -4449,7 +4449,7 @@
         <v>43404</v>
       </c>
       <c r="B155" t="n">
-        <v>66.53398132324219</v>
+        <v>66.53398895263672</v>
       </c>
       <c r="C155" t="n">
         <v>75.04000091552734</v>
@@ -4478,7 +4478,7 @@
         <v>43434</v>
       </c>
       <c r="B156" t="n">
-        <v>66.80258178710938</v>
+        <v>66.80260467529297</v>
       </c>
       <c r="C156" t="n">
         <v>75.12000274658203</v>
@@ -4536,7 +4536,7 @@
         <v>43496</v>
       </c>
       <c r="B158" t="n">
-        <v>72.81410980224609</v>
+        <v>72.81411743164062</v>
       </c>
       <c r="C158" t="n">
         <v>81.87999725341797</v>
@@ -4565,7 +4565,7 @@
         <v>43524</v>
       </c>
       <c r="B159" t="n">
-        <v>76.23785400390625</v>
+        <v>76.23783874511719</v>
       </c>
       <c r="C159" t="n">
         <v>85.73000335693359</v>
@@ -4652,7 +4652,7 @@
         <v>43616</v>
       </c>
       <c r="B162" t="n">
-        <v>68.96685791015625</v>
+        <v>68.96688842773438</v>
       </c>
       <c r="C162" t="n">
         <v>77.13999938964844</v>
@@ -4681,7 +4681,7 @@
         <v>43646</v>
       </c>
       <c r="B163" t="n">
-        <v>75.05531311035156</v>
+        <v>75.05532836914062</v>
       </c>
       <c r="C163" t="n">
         <v>83.94999694824219</v>
@@ -4710,7 +4710,7 @@
         <v>43677</v>
       </c>
       <c r="B164" t="n">
-        <v>76.91495513916016</v>
+        <v>76.91493988037109</v>
       </c>
       <c r="C164" t="n">
         <v>86.02999877929688</v>
@@ -4739,7 +4739,7 @@
         <v>43708</v>
       </c>
       <c r="B165" t="n">
-        <v>75.74222564697266</v>
+        <v>75.74224090576172</v>
       </c>
       <c r="C165" t="n">
         <v>84.5</v>
@@ -4768,7 +4768,7 @@
         <v>43738</v>
       </c>
       <c r="B166" t="n">
-        <v>84.18593597412109</v>
+        <v>84.18592071533203</v>
       </c>
       <c r="C166" t="n">
         <v>93.91999816894531</v>
@@ -4797,7 +4797,7 @@
         <v>43769</v>
       </c>
       <c r="B167" t="n">
-        <v>80.26883697509766</v>
+        <v>80.26882934570312</v>
       </c>
       <c r="C167" t="n">
         <v>89.55000305175781</v>
@@ -4826,7 +4826,7 @@
         <v>43799</v>
       </c>
       <c r="B168" t="n">
-        <v>84.01912689208984</v>
+        <v>84.01915740966797</v>
       </c>
       <c r="C168" t="n">
         <v>93.48999786376953</v>
@@ -4855,7 +4855,7 @@
         <v>43830</v>
       </c>
       <c r="B169" t="n">
-        <v>91.04695129394531</v>
+        <v>91.04694366455078</v>
       </c>
       <c r="C169" t="n">
         <v>101.3099975585938</v>
@@ -4884,7 +4884,7 @@
         <v>43861</v>
       </c>
       <c r="B170" t="n">
-        <v>86.54448699951172</v>
+        <v>86.54447174072266</v>
       </c>
       <c r="C170" t="n">
         <v>96.30000305175781</v>
@@ -4913,7 +4913,7 @@
         <v>43890</v>
       </c>
       <c r="B171" t="n">
-        <v>80.54835510253906</v>
+        <v>80.54833221435547</v>
       </c>
       <c r="C171" t="n">
         <v>89.37999725341797</v>
@@ -4942,7 +4942,7 @@
         <v>43921</v>
       </c>
       <c r="B172" t="n">
-        <v>74.56444549560547</v>
+        <v>74.564453125</v>
       </c>
       <c r="C172" t="n">
         <v>82.73999786376953</v>
@@ -4971,7 +4971,7 @@
         <v>43951</v>
       </c>
       <c r="B173" t="n">
-        <v>78.56573486328125</v>
+        <v>78.56575012207031</v>
       </c>
       <c r="C173" t="n">
         <v>87.18000030517578</v>
@@ -5058,7 +5058,7 @@
         <v>44043</v>
       </c>
       <c r="B176" t="n">
-        <v>88.18457794189453</v>
+        <v>88.18458557128906</v>
       </c>
       <c r="C176" t="n">
         <v>97.61000061035156</v>
@@ -5087,7 +5087,7 @@
         <v>44074</v>
       </c>
       <c r="B177" t="n">
-        <v>101.3096084594727</v>
+        <v>101.3096160888672</v>
       </c>
       <c r="C177" t="n">
         <v>111.8899993896484</v>
@@ -5116,7 +5116,7 @@
         <v>44104</v>
       </c>
       <c r="B178" t="n">
-        <v>113.6688613891602</v>
+        <v>113.6688690185547</v>
       </c>
       <c r="C178" t="n">
         <v>125.5400009155273</v>
@@ -5145,7 +5145,7 @@
         <v>44135</v>
       </c>
       <c r="B179" t="n">
-        <v>108.7251586914062</v>
+        <v>108.7251663208008</v>
       </c>
       <c r="C179" t="n">
         <v>120.0800018310547</v>
@@ -5174,7 +5174,7 @@
         <v>44165</v>
       </c>
       <c r="B180" t="n">
-        <v>121.9626922607422</v>
+        <v>121.9626846313477</v>
       </c>
       <c r="C180" t="n">
         <v>134.6999969482422</v>
@@ -5203,7 +5203,7 @@
         <v>44196</v>
       </c>
       <c r="B181" t="n">
-        <v>128.3502349853516</v>
+        <v>128.3502044677734</v>
       </c>
       <c r="C181" t="n">
         <v>141.4700012207031</v>
@@ -5232,7 +5232,7 @@
         <v>44227</v>
       </c>
       <c r="B182" t="n">
-        <v>121.2009887695312</v>
+        <v>121.2010040283203</v>
       </c>
       <c r="C182" t="n">
         <v>133.5899963378906</v>
@@ -5261,7 +5261,7 @@
         <v>44255</v>
       </c>
       <c r="B183" t="n">
-        <v>122.5292205810547</v>
+        <v>122.5292358398438</v>
       </c>
       <c r="C183" t="n">
         <v>134.7799987792969</v>
@@ -5290,7 +5290,7 @@
         <v>44286</v>
       </c>
       <c r="B184" t="n">
-        <v>120.8110504150391</v>
+        <v>120.81103515625</v>
       </c>
       <c r="C184" t="n">
         <v>132.8899993896484</v>
@@ -5319,7 +5319,7 @@
         <v>44316</v>
       </c>
       <c r="B185" t="n">
-        <v>120.5655975341797</v>
+        <v>120.5655899047852</v>
       </c>
       <c r="C185" t="n">
         <v>132.6199951171875</v>
@@ -5348,7 +5348,7 @@
         <v>44347</v>
       </c>
       <c r="B186" t="n">
-        <v>124.3068771362305</v>
+        <v>124.3068695068359</v>
       </c>
       <c r="C186" t="n">
         <v>136.4600067138672</v>
@@ -5377,7 +5377,7 @@
         <v>44377</v>
       </c>
       <c r="B187" t="n">
-        <v>140.7310943603516</v>
+        <v>140.7311248779297</v>
       </c>
       <c r="C187" t="n">
         <v>154.4900054931641</v>
@@ -5406,7 +5406,7 @@
         <v>44408</v>
       </c>
       <c r="B188" t="n">
-        <v>152.5915374755859</v>
+        <v>152.5915222167969</v>
       </c>
       <c r="C188" t="n">
         <v>167.5099945068359</v>
@@ -5435,7 +5435,7 @@
         <v>44439</v>
       </c>
       <c r="B189" t="n">
-        <v>150.3159027099609</v>
+        <v>150.3158874511719</v>
       </c>
       <c r="C189" t="n">
         <v>164.7400054931641</v>
@@ -5464,7 +5464,7 @@
         <v>44469</v>
       </c>
       <c r="B190" t="n">
-        <v>132.5141296386719</v>
+        <v>132.51416015625</v>
       </c>
       <c r="C190" t="n">
         <v>145.2299957275391</v>
@@ -5493,7 +5493,7 @@
         <v>44500</v>
       </c>
       <c r="B191" t="n">
-        <v>152.6425933837891</v>
+        <v>152.6426391601562</v>
       </c>
       <c r="C191" t="n">
         <v>167.2899932861328</v>
@@ -5522,7 +5522,7 @@
         <v>44530</v>
       </c>
       <c r="B192" t="n">
-        <v>154.4219055175781</v>
+        <v>154.4218902587891</v>
       </c>
       <c r="C192" t="n">
         <v>169.2400054931641</v>
@@ -5551,7 +5551,7 @@
         <v>44561</v>
       </c>
       <c r="B193" t="n">
-        <v>152.3502655029297</v>
+        <v>152.3502349853516</v>
       </c>
       <c r="C193" t="n">
         <v>166.6699981689453</v>
@@ -5580,7 +5580,7 @@
         <v>44592</v>
       </c>
       <c r="B194" t="n">
-        <v>135.3482971191406</v>
+        <v>135.3483123779297</v>
       </c>
       <c r="C194" t="n">
         <v>148.0700073242188</v>
@@ -5609,7 +5609,7 @@
         <v>44620</v>
       </c>
       <c r="B195" t="n">
-        <v>124.8180465698242</v>
+        <v>124.8180541992188</v>
       </c>
       <c r="C195" t="n">
         <v>136.5500030517578</v>
@@ -5638,7 +5638,7 @@
         <v>44651</v>
       </c>
       <c r="B196" t="n">
-        <v>123.279670715332</v>
+        <v>123.2796936035156</v>
       </c>
       <c r="C196" t="n">
         <v>134.5599975585938</v>
@@ -5667,7 +5667,7 @@
         <v>44681</v>
       </c>
       <c r="B197" t="n">
-        <v>114.2462692260742</v>
+        <v>114.2462539672852</v>
       </c>
       <c r="C197" t="n">
         <v>124.6999969482422</v>
@@ -5696,7 +5696,7 @@
         <v>44712</v>
       </c>
       <c r="B198" t="n">
-        <v>108.8866882324219</v>
+        <v>108.8866729736328</v>
       </c>
       <c r="C198" t="n">
         <v>118.8499984741211</v>
@@ -5783,7 +5783,7 @@
         <v>44804</v>
       </c>
       <c r="B201" t="n">
-        <v>97.76781463623047</v>
+        <v>97.76780700683594</v>
       </c>
       <c r="C201" t="n">
         <v>106.4499969482422</v>
@@ -5812,7 +5812,7 @@
         <v>44834</v>
       </c>
       <c r="B202" t="n">
-        <v>76.55992126464844</v>
+        <v>76.55990600585938</v>
       </c>
       <c r="C202" t="n">
         <v>83.12000274658203</v>
@@ -5899,7 +5899,7 @@
         <v>44926</v>
       </c>
       <c r="B205" t="n">
-        <v>108.1060104370117</v>
+        <v>108.1060180664062</v>
       </c>
       <c r="C205" t="n">
         <v>117.0100021362305</v>
@@ -5928,7 +5928,7 @@
         <v>44957</v>
       </c>
       <c r="B206" t="n">
-        <v>117.6407012939453</v>
+        <v>117.6407089233398</v>
       </c>
       <c r="C206" t="n">
         <v>127.3300018310547</v>
@@ -5957,7 +5957,7 @@
         <v>44985</v>
       </c>
       <c r="B207" t="n">
-        <v>109.7505493164062</v>
+        <v>109.7505722045898</v>
       </c>
       <c r="C207" t="n">
         <v>118.7900009155273</v>
@@ -5986,7 +5986,7 @@
         <v>45016</v>
       </c>
       <c r="B208" t="n">
-        <v>113.6306610107422</v>
+        <v>113.6306838989258</v>
       </c>
       <c r="C208" t="n">
         <v>122.6399993896484</v>
@@ -6044,7 +6044,7 @@
         <v>45077</v>
       </c>
       <c r="B210" t="n">
-        <v>97.52744293212891</v>
+        <v>97.52745056152344</v>
       </c>
       <c r="C210" t="n">
         <v>105.2600021362305</v>
@@ -6073,7 +6073,7 @@
         <v>45107</v>
       </c>
       <c r="B211" t="n">
-        <v>102.5986862182617</v>
+        <v>102.5986709594727</v>
       </c>
       <c r="C211" t="n">
         <v>110.370002746582</v>
@@ -6102,7 +6102,7 @@
         <v>45138</v>
       </c>
       <c r="B212" t="n">
-        <v>102.6172485351562</v>
+        <v>102.6172637939453</v>
       </c>
       <c r="C212" t="n">
         <v>110.3899993896484</v>
@@ -6160,7 +6160,7 @@
         <v>45199</v>
       </c>
       <c r="B214" t="n">
-        <v>89.18537902832031</v>
+        <v>89.18537139892578</v>
       </c>
       <c r="C214" t="n">
         <v>95.62000274658203</v>
@@ -6189,7 +6189,7 @@
         <v>45230</v>
       </c>
       <c r="B215" t="n">
-        <v>95.85423278808594</v>
+        <v>95.85420227050781</v>
       </c>
       <c r="C215" t="n">
         <v>102.7699966430664</v>
@@ -6218,7 +6218,7 @@
         <v>45260</v>
       </c>
       <c r="B216" t="n">
-        <v>102.8495178222656</v>
+        <v>102.8495254516602</v>
       </c>
       <c r="C216" t="n">
         <v>110.2699966430664</v>
@@ -6276,7 +6276,7 @@
         <v>45322</v>
       </c>
       <c r="B218" t="n">
-        <v>95.01649475097656</v>
+        <v>95.01648712158203</v>
       </c>
       <c r="C218" t="n">
         <v>101.5299987792969</v>
@@ -6363,7 +6363,7 @@
         <v>45412</v>
       </c>
       <c r="B221" t="n">
-        <v>86.64966583251953</v>
+        <v>86.64967346191406</v>
       </c>
       <c r="C221" t="n">
         <v>92.26000213623047</v>
@@ -6421,7 +6421,7 @@
         <v>45473</v>
       </c>
       <c r="B223" t="n">
-        <v>71.06336975097656</v>
+        <v>71.06337738037109</v>
       </c>
       <c r="C223" t="n">
         <v>75.37000274658203</v>
@@ -6450,7 +6450,7 @@
         <v>45504</v>
       </c>
       <c r="B224" t="n">
-        <v>70.58251190185547</v>
+        <v>70.58251953125</v>
       </c>
       <c r="C224" t="n">
         <v>74.86000061035156</v>
@@ -6479,7 +6479,7 @@
         <v>45535</v>
       </c>
       <c r="B225" t="n">
-        <v>78.55910491943359</v>
+        <v>78.55911254882812</v>
       </c>
       <c r="C225" t="n">
         <v>83.31999969482422</v>
@@ -6537,7 +6537,7 @@
         <v>45596</v>
       </c>
       <c r="B227" t="n">
-        <v>73.04718780517578</v>
+        <v>73.04719543457031</v>
       </c>
       <c r="C227" t="n">
         <v>77.12999725341797</v>
@@ -6595,7 +6595,7 @@
         <v>45657</v>
       </c>
       <c r="B229" t="n">
-        <v>72.03025054931641</v>
+        <v>72.03024291992188</v>
       </c>
       <c r="C229" t="n">
         <v>75.66999816894531</v>
@@ -6624,7 +6624,7 @@
         <v>45688</v>
       </c>
       <c r="B230" t="n">
-        <v>73.20108032226562</v>
+        <v>73.20108795166016</v>
       </c>
       <c r="C230" t="n">
         <v>76.90000152587891</v>
@@ -6653,7 +6653,7 @@
         <v>45716</v>
       </c>
       <c r="B231" t="n">
-        <v>75.60939788818359</v>
+        <v>75.60939025878906</v>
       </c>
       <c r="C231" t="n">
         <v>79.43000030517578</v>
@@ -6740,7 +6740,7 @@
         <v>45808</v>
       </c>
       <c r="B234" t="n">
-        <v>57.96752166748047</v>
+        <v>57.9675178527832</v>
       </c>
       <c r="C234" t="n">
         <v>60.59000015258789</v>
@@ -6827,7 +6827,7 @@
         <v>45900</v>
       </c>
       <c r="B237" t="n">
-        <v>74.51315307617188</v>
+        <v>74.51316070556641</v>
       </c>
       <c r="C237" t="n">
         <v>77.37000274658203</v>
@@ -6885,7 +6885,7 @@
         <v>45961</v>
       </c>
       <c r="B239" t="n">
-        <v>62.5283203125</v>
+        <v>62.52831268310547</v>
       </c>
       <c r="C239" t="n">
         <v>64.58999633789062</v>
@@ -6914,7 +6914,7 @@
         <v>45991</v>
       </c>
       <c r="B240" t="n">
-        <v>62.56704330444336</v>
+        <v>62.56704711914062</v>
       </c>
       <c r="C240" t="n">
         <v>64.62999725341797</v>
@@ -6943,7 +6943,7 @@
         <v>46022</v>
       </c>
       <c r="B241" t="n">
-        <v>62.07016754150391</v>
+        <v>62.07017135620117</v>
       </c>
       <c r="C241" t="n">
         <v>63.70999908447266</v>
@@ -6972,7 +6972,7 @@
         <v>46053</v>
       </c>
       <c r="B242" t="n">
-        <v>60.21907424926758</v>
+        <v>60.21907043457031</v>
       </c>
       <c r="C242" t="n">
         <v>61.81000137329102</v>
@@ -7001,7 +7001,7 @@
         <v>46081</v>
       </c>
       <c r="B243" t="n">
-        <v>60.57955169677734</v>
+        <v>60.57954788208008</v>
       </c>
       <c r="C243" t="n">
         <v>62.18000030517578</v>
@@ -7059,7 +7059,7 @@
         <v>46142</v>
       </c>
       <c r="B245" t="n">
-        <v>43.50508117675781</v>
+        <v>43.50508499145508</v>
       </c>
       <c r="C245" t="n">
         <v>44.36000061035156</v>
